--- a/public/model/v1/current/knowledge_model_package_v1.xlsx
+++ b/public/model/v1/current/knowledge_model_package_v1.xlsx
@@ -14,10 +14,14 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4.Соответствие полей" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5.Маршрут миграции" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6.План отката" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7.RBAC" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7.RBAC (целевая модель)" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8.Безопасность RAG" sheetId="9" state="visible" r:id="rId9"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="9.ADR-реестр" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10.Границы этапа 1" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10.Decision Log" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11.Аудит AI-маршрута" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12.Issue Register" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="13.Risk Register" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="14.Границы этапа 1" sheetId="15" state="visible" r:id="rId15"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -27,7 +31,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="11">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -47,11 +51,6 @@
     <font>
       <b val="1"/>
       <sz val="10.5"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="10"/>
     </font>
     <font>
       <b val="1"/>
@@ -76,6 +75,8 @@
     </font>
     <font>
       <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="7">
@@ -92,12 +93,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D5E8D4"/>
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
+        <fgColor rgb="00D5E8D4"/>
       </patternFill>
     </fill>
     <fill>
@@ -137,26 +138,23 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -165,7 +163,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -534,14 +531,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E51"/>
+  <dimension ref="A1:A60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="110" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="112" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -554,485 +547,359 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Версия: v1  ·  Статус: Draft / На рассмотрении  ·  Автор: Юра (AI-разработчик)  ·  Дата: 2026-09-11</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr"/>
-    </row>
+          <t>Версия: v2  ·  Статус: Draft / На рассмотрении  ·  Автор: Юра (AI-разработчик)  ·  Дата: 2026-09-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>НАЗНАЧЕНИЕ</t>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>ЧТО ИЗМЕНИЛОСЬ С v1</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Проектный пакет описывает целевую модель документов, знаний, статусов и доступа для кабинета ЦЦиРТКД.</t>
+          <t>— добавлен read-only аудит фактического маршрута данных в AI-провайдера (лист 11);</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Пакет НЕ является техническим заданием и НЕ содержит оценки трудозатрат.</t>
+          <t>— решения разделены на 4 отдельных реестра: ADR / Decision Log / Issue Register / Risk Register;</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr"/>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>— ADR-008 (приостановка анализа 145 записей ДФМ) перенесён из ADR в Decision Log — это управленческое,</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>ГРАНИЦЫ АНАЛИЗА</t>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  а не архитектурное решение;</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>В пакет вошли: 6 записей exec_knowledge, справочник bank_function_catalog (67 строк),</t>
+          <t>— формулировки о 'блокировке' и 'ИИ не может утверждать' переквалифицированы: это ЦЕЛЕВОЕ требование,</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>структура exec_center_function, org_units, прямой потребитель exec-planner-ai.</t>
+          <t xml:space="preserve">  техническая реализация отсутствует — см. лист 11 и Risk Register;</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>В пакет НЕ вошли: 145 записей dept_functions (ДФМ) — исследование приостановлено по решению руководителя,</t>
+          <t>— контрольная сумма XLSX вынесена из самого файла во внешний MANIFEST.sha256 (вне XLSX);</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>портфель инициатив/проектов, полный редизайн кабинета, облачные функции, презентации.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr"/>
-    </row>
+          <t>— архив всех файлов собран в один ZIP для передачи вне среды разработки.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>ИСПОЛЬЗОВАННЫЕ ИСТОЧНИКИ</t>
+          <t>НАЗНАЧЕНИЕ ПАКЕТА</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>— прямые SQL-запросы к БД проекта — факты о структуре и данных;</t>
+          <t>Проектный пакет описывает целевую модель документов, знаний, статусов и доступа для кабинета ЦЦиРТКД.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>— чтение исходного кода backend/exec-knowledge/index.py, backend/exec-planner-ai/index.py — факты о логике;</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>— HEAD-запросы к публичному CDN — проверка доступности файлов ПО СОХРАНЁННОЙ ССЫЛКЕ (не через API хранилища);</t>
-        </is>
-      </c>
-    </row>
+          <t>Пакет НЕ является техническим заданием и НЕ содержит оценки трудозатрат.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17"/>
     <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>— грепы по /src — факты об использовании API во фронтенде.</t>
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>ГРАНИЦЫ АНАЛИЗА</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr"/>
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>В пакет вошли: 6 записей exec_knowledge, справочник bank_function_catalog (67 строк),</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>УСТАНОВЛЕННЫЕ ФАКТЫ (проверено, не предположение)</t>
+          <t>структура exec_center_function, org_units, backend exec-planner-ai (включая аудит вызова AI-провайдера).</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>— в exec_knowledge 6 записей, у 1 из 6 подтверждён физический файл (id=2, 42638 байт);</t>
+          <t>В пакет НЕ вошли: 145 записей dept_functions (ДФМ) — приостановлено, см. Decision Log DL-001;</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>— в exec-knowledge/index.py отсутствуют поля и код для классификации конфиденциальности,</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  разграничения доступа на уровне документа, журналирования чтения (проверено по исходному коду модуля);</t>
-        </is>
-      </c>
-    </row>
+          <t>портфель инициатив/проектов, полный редизайн кабинета, облачные функции, презентации.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23"/>
     <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>— exec-planner-ai — единственный обнаруженный backend-потребитель содержания exec_knowledge для AI-контекста;</t>
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>ИСТОЧНИКИ</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>— exec_source_document и exec_source_usage существуют в схеме БД, но содержат 0 записей;</t>
+          <t>— прямые SQL-запросы к БД проекта; чтение исходного кода backend/exec-knowledge, backend/exec-planner-ai;</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>— documents (17 записей) относится к модулю 'Проекты' (дипломная работа, учебные материалы),</t>
+          <t>— HEAD-запросы к публичному CDN (проверка ПО ССЫЛКЕ, не через API хранилища); грепы по /src;</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t xml:space="preserve">  не к контуру ЦЦиРТКД — прежнее сравнение с exec_knowledge как 'два контура одной сущности' ошибочно;</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>— коды 81.42 и 81.342 отсутствуют в bank_function_catalog (67 строк) при использовании в exec_center_function.</t>
-        </is>
-      </c>
-    </row>
+          <t>— список секретов проекта (только имена, без значений) для определения используемого AI-провайдера.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28"/>
     <row r="29">
-      <c r="A29" t="inlineStr"/>
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>КЛЮЧЕВОЙ ФАКТ АУДИТА (новое в v2)</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>ПРЕДПОЛОЖЕНИЯ И ОГРАНИЧЕНИЯ (НЕ факты)</t>
+          <t>Все 6 записей exec_knowledge имеют use_in_ai=true. Фильтра, исключающего конфиденциальные документы</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>— происхождение 145 записей dept_functions НЕ установлено — статус зафиксирован как 'не установлено',</t>
+          <t>из payload в YandexGPT, в коде НЕТ. Технической блокировки передачи ВНД во внешний AI не существует —</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t xml:space="preserve">  дальнейшее исследование приостановлено по решению руководителя;</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>— отсутствие полей безопасности В МОДУЛЕ exec-knowledge НЕ доказывает отсутствие компенсирующих механизмов</t>
-        </is>
-      </c>
-    </row>
+          <t>см. лист 11 'Аудит AI-маршрута' и Risk Register RR-001.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33"/>
     <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  на общесистемном/инфраструктурном уровне — не проверялось;</t>
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>УСТАНОВЛЕННЫЕ ФАКТЫ</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>— HEAD-запрос к CDN подтверждает недоступность ПО СОХРАНЁННОЙ ССЫЛКЕ, не факт физического отсутствия объекта</t>
+          <t>— в exec_knowledge 6 записей, у 1 из 6 подтверждён физический файл (id=2, 42638 байт);</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t xml:space="preserve">  в хранилище — проверка через служебный API провайдера не проводилась (нет технической возможности в песочнице);</t>
+          <t>— используемый AI-провайдер — YandexGPT (llm.api.cloud.yandex.net), единственный секрет YANDEX_GPT_API_KEY;</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>— способ и субъект создания 145 записей ДФМ и части других массивов не установлены достоверно.</t>
+          <t>— exec-planner-ai не ведёт журнал запросов к AI-провайдеру: ни в БД, ни через logger/print в коде;</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr"/>
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>— get_logs по backend/exec-planner-ai не вернул записей — установить факт прошлых вызовов невозможно;</t>
+        </is>
+      </c>
     </row>
     <row r="39">
-      <c r="A39" s="3" t="inlineStr">
-        <is>
-          <t>СОСТАВ ФАЙЛОВ ПАКЕТА</t>
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>— в exec-knowledge/index.py отсутствуют поля конфиденциальности, доступа по документу, журнала чтения;</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="4" t="inlineStr">
-        <is>
-          <t>Файл</t>
-        </is>
-      </c>
-      <c r="B40" s="4" t="inlineStr">
-        <is>
-          <t>Формат</t>
-        </is>
-      </c>
-      <c r="C40" s="4" t="inlineStr">
-        <is>
-          <t>Размер, байт</t>
-        </is>
-      </c>
-      <c r="D40" s="4" t="inlineStr">
-        <is>
-          <t>SHA-256 (16 симв.)</t>
-        </is>
-      </c>
-      <c r="E40" s="4" t="inlineStr">
-        <is>
-          <t>Статус</t>
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>— exec_source_document и exec_source_usage существуют в схеме БД, но содержат 0 записей;</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="5" t="inlineStr">
-        <is>
-          <t>er_as_is_v1.mmd</t>
-        </is>
-      </c>
-      <c r="B41" s="5" t="inlineStr">
-        <is>
-          <t>MMD</t>
-        </is>
-      </c>
-      <c r="C41" s="5" t="n">
-        <v>3638</v>
-      </c>
-      <c r="D41" s="5" t="inlineStr">
-        <is>
-          <t>57d48b8c50f67dff</t>
-        </is>
-      </c>
-      <c r="E41" s="6" t="inlineStr">
-        <is>
-          <t>актуальный</t>
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>— documents (17 записей) относится к модулю 'Проекты', не к контуру ЦЦиРТКД;</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="5" t="inlineStr">
-        <is>
-          <t>er_as_is_v1.png</t>
-        </is>
-      </c>
-      <c r="B42" s="5" t="inlineStr">
-        <is>
-          <t>PNG</t>
-        </is>
-      </c>
-      <c r="C42" s="5" t="n">
-        <v>217250</v>
-      </c>
-      <c r="D42" s="5" t="inlineStr">
-        <is>
-          <t>32e7e2d259d516f7</t>
-        </is>
-      </c>
-      <c r="E42" s="6" t="inlineStr">
-        <is>
-          <t>актуальный</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="5" t="inlineStr">
-        <is>
-          <t>er_to_be_v1.mmd</t>
-        </is>
-      </c>
-      <c r="B43" s="5" t="inlineStr">
-        <is>
-          <t>MMD</t>
-        </is>
-      </c>
-      <c r="C43" s="5" t="n">
-        <v>2718</v>
-      </c>
-      <c r="D43" s="5" t="inlineStr">
-        <is>
-          <t>7a9639f91330d713</t>
-        </is>
-      </c>
-      <c r="E43" s="6" t="inlineStr">
-        <is>
-          <t>актуальный</t>
-        </is>
-      </c>
-    </row>
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>— коды 81.42 и 81.342 отсутствуют в bank_function_catalog при использовании в exec_center_function.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43"/>
     <row r="44">
-      <c r="A44" s="5" t="inlineStr">
-        <is>
-          <t>er_to_be_v1.png</t>
-        </is>
-      </c>
-      <c r="B44" s="5" t="inlineStr">
-        <is>
-          <t>PNG</t>
-        </is>
-      </c>
-      <c r="C44" s="5" t="n">
-        <v>257612</v>
-      </c>
-      <c r="D44" s="5" t="inlineStr">
-        <is>
-          <t>690cf3fecdee45d9</t>
-        </is>
-      </c>
-      <c r="E44" s="6" t="inlineStr">
-        <is>
-          <t>актуальный</t>
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>ПРЕДПОЛОЖЕНИЯ И ОГРАНИЧЕНИЯ (НЕ факты)</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="5" t="inlineStr">
-        <is>
-          <t>status_model_document_v1.mmd</t>
-        </is>
-      </c>
-      <c r="B45" s="5" t="inlineStr">
-        <is>
-          <t>MMD</t>
-        </is>
-      </c>
-      <c r="C45" s="5" t="n">
-        <v>2309</v>
-      </c>
-      <c r="D45" s="5" t="inlineStr">
-        <is>
-          <t>effd2407f4cec7a1</t>
-        </is>
-      </c>
-      <c r="E45" s="6" t="inlineStr">
-        <is>
-          <t>актуальный</t>
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>— происхождение 145 записей dept_functions НЕ установлено, исследование приостановлено (DL-001);</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="5" t="inlineStr">
-        <is>
-          <t>status_model_document_v1.png</t>
-        </is>
-      </c>
-      <c r="B46" s="5" t="inlineStr">
-        <is>
-          <t>PNG</t>
-        </is>
-      </c>
-      <c r="C46" s="5" t="n">
-        <v>158565</v>
-      </c>
-      <c r="D46" s="5" t="inlineStr">
-        <is>
-          <t>3649f3ba97c8bd5d</t>
-        </is>
-      </c>
-      <c r="E46" s="6" t="inlineStr">
-        <is>
-          <t>актуальный</t>
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>— отсутствие полей безопасности В МОДУЛЕ exec-knowledge не доказывает отсутствие компенсирующих мер</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="5" t="inlineStr">
-        <is>
-          <t>status_model_general_entities_v1.png</t>
-        </is>
-      </c>
-      <c r="B47" s="5" t="inlineStr">
-        <is>
-          <t>PNG</t>
-        </is>
-      </c>
-      <c r="C47" s="5" t="n">
-        <v>179951</v>
-      </c>
-      <c r="D47" s="5" t="inlineStr">
-        <is>
-          <t>425caf55be9355df</t>
-        </is>
-      </c>
-      <c r="E47" s="6" t="inlineStr">
-        <is>
-          <t>актуальный</t>
+      <c r="A47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  на общесистемном/инфраструктурном уровне — не проверялось;</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="5" t="inlineStr">
-        <is>
-          <t>knowledge_model_package_v1.xlsx</t>
-        </is>
-      </c>
-      <c r="B48" s="5" t="inlineStr">
-        <is>
-          <t>XLSX</t>
-        </is>
-      </c>
-      <c r="C48" s="5" t="inlineStr">
-        <is>
-          <t>(этот файл)</t>
-        </is>
-      </c>
-      <c r="D48" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E48" s="6" t="inlineStr">
-        <is>
-          <t>актуальный</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="3" t="inlineStr">
-        <is>
-          <t>ЖУРНАЛ ВЕРСИЙ</t>
-        </is>
-      </c>
-    </row>
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>— HEAD-запрос к CDN подтверждает недоступность ПО ССЫЛКЕ, не факт отсутствия в хранилище;</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>— были ли документы уже фактически переданы в YandexGPT ранее — установить невозможно (нет журнала).</t>
+        </is>
+      </c>
+    </row>
+    <row r="50"/>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>v1 — 2026-09-11 — первая версия пакета после раунда правок (legacy/shadow/canonical, RBAC, ADR-реестр, манифест)</t>
+          <t>ТЕХНИЧЕСКАЯ ВАЛИДАЦИЯ ПАКЕТА (самопроверка Юры, требует вашей независимой проверки)</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>— knowledge_model_package_v1.xlsx: открыт локально после сборки, все 14 листов на месте, ошибок нет;</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>*.mmd файлы: синтаксис проверен вручную построчным разбором ER/state-нотации (парность скобок сущностей с учётом нотации кратности связей ||--o{ и }o--o{) — расхождений не найдено. Полную автокомпиляцию через mermaid-cli не выполнял (недоступен в среде) — рекомендую дополнительно открыть на mermaid.live перед утверждением;</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  не выполнял — рекомендую проверить на mermaid.live перед утверждением;</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>— *.png сгенерированы напрямую скриптами matplotlib, НЕ из .mmd — это два независимых представления</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  одной и той же модели, сверка 'картинка = рендер исходника' не выполнялась и не может быть выполнена</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  автоматически без mermaid-cli; расхождения между .mmd и .png не исключены;</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>— контрольные суммы всех файлов пакета — во внешнем MANIFEST.sha256, НЕ внутри XLSX.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59"/>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>СОСТАВ ФАЙЛОВ ПАКЕТА — см. MANIFEST.sha256 в архиве</t>
         </is>
       </c>
     </row>
@@ -1047,546 +914,358 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I14"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="36" customWidth="1" min="3" max="3"/>
-    <col width="40" customWidth="1" min="4" max="4"/>
-    <col width="34" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="26" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
+    <col width="38" customWidth="1" min="5" max="5"/>
+    <col width="32" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="10" t="inlineStr">
+      <c r="A1" s="7" t="inlineStr">
         <is>
           <t>Реестр архитектурных решений (ADR)</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="11" t="inlineStr">
-        <is>
-          <t>'не принято' = решение на рассмотрении руководителя, в базу и код не внесено</t>
+      <c r="A2" s="8" t="inlineStr">
+        <is>
+          <t>Только решения, определяющие устройство системы. Управленческие решения — см. Decision Log (лист 10)</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="12" t="inlineStr">
+      <c r="A4" s="9" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B4" s="12" t="inlineStr">
+      <c r="B4" s="9" t="inlineStr">
+        <is>
+          <t>Категория</t>
+        </is>
+      </c>
+      <c r="C4" s="9" t="inlineStr">
         <is>
           <t>Вопрос</t>
         </is>
       </c>
-      <c r="C4" s="12" t="inlineStr">
+      <c r="D4" s="9" t="inlineStr">
         <is>
           <t>Варианты</t>
         </is>
       </c>
-      <c r="D4" s="12" t="inlineStr">
+      <c r="E4" s="9" t="inlineStr">
         <is>
           <t>Рекомендация</t>
         </is>
       </c>
-      <c r="E4" s="12" t="inlineStr">
+      <c r="F4" s="9" t="inlineStr">
         <is>
           <t>Последствия</t>
         </is>
       </c>
-      <c r="F4" s="12" t="inlineStr">
+      <c r="G4" s="9" t="inlineStr">
         <is>
           <t>Риск</t>
         </is>
       </c>
-      <c r="G4" s="12" t="inlineStr">
-        <is>
-          <t>Владелец решения</t>
-        </is>
-      </c>
-      <c r="H4" s="12" t="inlineStr">
-        <is>
-          <t>Срок</t>
-        </is>
-      </c>
-      <c r="I4" s="12" t="inlineStr">
-        <is>
-          <t>Итоговый статус</t>
+      <c r="H4" s="9" t="inlineStr">
+        <is>
+          <t>Владелец</t>
+        </is>
+      </c>
+      <c r="I4" s="9" t="inlineStr">
+        <is>
+          <t>Статус</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="13" t="inlineStr">
+      <c r="A5" s="10" t="inlineStr">
         <is>
           <t>ADR-001</t>
         </is>
       </c>
-      <c r="B5" s="13" t="inlineStr">
-        <is>
-          <t>Статус записи №2 (О создании рабочей группы)</t>
-        </is>
-      </c>
-      <c r="C5" s="13" t="inlineStr">
-        <is>
-          <t>Признать кандидатом сразу / только после сверки хеша и метаданных</t>
-        </is>
-      </c>
-      <c r="D5" s="13" t="inlineStr">
-        <is>
-          <t>Только после сверки хеша, метаданных и соответствия извлечённого текста оригиналу</t>
-        </is>
-      </c>
-      <c r="E5" s="13" t="inlineStr">
-        <is>
-          <t>Задержка присвоения статуса на время проверки</t>
-        </is>
-      </c>
-      <c r="F5" s="13" t="inlineStr">
+      <c r="B5" s="10" t="inlineStr">
+        <is>
+          <t>Архитектура</t>
+        </is>
+      </c>
+      <c r="C5" s="10" t="inlineStr">
+        <is>
+          <t>Модель хранения оригиналов документов</t>
+        </is>
+      </c>
+      <c r="D5" s="10" t="inlineStr">
+        <is>
+          <t>exec_source_document как единая точка входа / оставить exec_knowledge как есть</t>
+        </is>
+      </c>
+      <c r="E5" s="10" t="inlineStr">
+        <is>
+          <t>Единая точка входа, exec_knowledge переводится в legacy без удаления</t>
+        </is>
+      </c>
+      <c r="F5" s="10" t="inlineStr">
+        <is>
+          <t>Требует миграции 6 записей и доработки exec-planner-ai</t>
+        </is>
+      </c>
+      <c r="G5" s="10" t="inlineStr">
+        <is>
+          <t>Средний</t>
+        </is>
+      </c>
+      <c r="H5" s="10" t="inlineStr">
+        <is>
+          <t>Архитектор/руководитель</t>
+        </is>
+      </c>
+      <c r="I5" s="10" t="inlineStr">
+        <is>
+          <t>не принято</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="10" t="inlineStr">
+        <is>
+          <t>ADR-002</t>
+        </is>
+      </c>
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>Архитектура</t>
+        </is>
+      </c>
+      <c r="C6" s="10" t="inlineStr">
+        <is>
+          <t>Правила shadow-режима перед переключением RAG-источника</t>
+        </is>
+      </c>
+      <c r="D6" s="10" t="inlineStr">
+        <is>
+          <t>Переключить сразу / вести теневую выборку заданный период</t>
+        </is>
+      </c>
+      <c r="E6" s="10" t="inlineStr">
+        <is>
+          <t>Shadow-период не менее 2 недель, сравнение контекста, релевантности, качества цитат</t>
+        </is>
+      </c>
+      <c r="F6" s="10" t="inlineStr">
+        <is>
+          <t>Отсрочка перехода в canonical</t>
+        </is>
+      </c>
+      <c r="G6" s="10" t="inlineStr">
         <is>
           <t>Низкий</t>
         </is>
       </c>
-      <c r="G5" s="13" t="inlineStr">
-        <is>
-          <t>Владелец документа</t>
-        </is>
-      </c>
-      <c r="H5" s="13" t="inlineStr">
-        <is>
-          <t>не установлен</t>
-        </is>
-      </c>
-      <c r="I5" s="13" t="inlineStr">
+      <c r="H6" s="10" t="inlineStr">
+        <is>
+          <t>Разработчик</t>
+        </is>
+      </c>
+      <c r="I6" s="10" t="inlineStr">
         <is>
           <t>не принято</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="13" t="inlineStr">
-        <is>
-          <t>ADR-002</t>
-        </is>
-      </c>
-      <c r="B6" s="13" t="inlineStr">
-        <is>
-          <t>Классификация записи №5 (заголовок 'официальный')</t>
-        </is>
-      </c>
-      <c r="C6" s="13" t="inlineStr">
-        <is>
-          <t>Оставить заголовок как есть / развести original_title и display_title</t>
-        </is>
-      </c>
-      <c r="D6" s="13" t="inlineStr">
-        <is>
-          <t>original_title сохраняется, display_title='Концепция роли CDS' без слова 'официальный'</t>
-        </is>
-      </c>
-      <c r="E6" s="13" t="inlineStr">
-        <is>
-          <t>Пользователи UI перестают видеть непроверенное слово 'официальный'</t>
-        </is>
-      </c>
-      <c r="F6" s="13" t="inlineStr">
-        <is>
-          <t>Средний (если не исправить)</t>
-        </is>
-      </c>
-      <c r="G6" s="13" t="inlineStr">
-        <is>
-          <t>Владелец документа</t>
-        </is>
-      </c>
-      <c r="H6" s="13" t="inlineStr">
-        <is>
-          <t>не установлен</t>
-        </is>
-      </c>
-      <c r="I6" s="13" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>ADR-003</t>
+        </is>
+      </c>
+      <c r="B7" s="10" t="inlineStr">
+        <is>
+          <t>Архитектура</t>
+        </is>
+      </c>
+      <c r="C7" s="10" t="inlineStr">
+        <is>
+          <t>Постраничная разметка legacy-записей без установленных страниц</t>
+        </is>
+      </c>
+      <c r="D7" s="10" t="inlineStr">
+        <is>
+          <t>Виртуальная страница 1 / page_number=NULL с locator_type</t>
+        </is>
+      </c>
+      <c r="E7" s="10" t="inlineStr">
+        <is>
+          <t>page_number=NULL, locator_type=legacy_text_offset, UI показывает 'страница не установлена'</t>
+        </is>
+      </c>
+      <c r="F7" s="10" t="inlineStr">
+        <is>
+          <t>Ответы ИИ не будут содержать ложных ссылок на страницу</t>
+        </is>
+      </c>
+      <c r="G7" s="10" t="inlineStr">
+        <is>
+          <t>Высокий (при неверном выборе)</t>
+        </is>
+      </c>
+      <c r="H7" s="10" t="inlineStr">
+        <is>
+          <t>Архитектор</t>
+        </is>
+      </c>
+      <c r="I7" s="10" t="inlineStr">
         <is>
           <t>не принято</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="13" t="inlineStr">
-        <is>
-          <t>ADR-003</t>
-        </is>
-      </c>
-      <c r="B7" s="13" t="inlineStr">
-        <is>
-          <t>Использование внешнего AI-провайдера для обработки ВНД Банка</t>
-        </is>
-      </c>
-      <c r="C7" s="13" t="inlineStr">
-        <is>
-          <t>Продолжить как есть / приостановить загрузку ВНД до проверки условий провайдера</t>
-        </is>
-      </c>
-      <c r="D7" s="13" t="inlineStr">
-        <is>
-          <t>Приостановить: не загружать новые ВНД и не индексировать в AI-поиск до отдельного решения</t>
-        </is>
-      </c>
-      <c r="E7" s="13" t="inlineStr">
-        <is>
-          <t>Блокирует расширение базы знаний до ответа юр./ИБ-службы</t>
-        </is>
-      </c>
-      <c r="F7" s="13" t="inlineStr">
-        <is>
-          <t>Критический — блокирующий</t>
-        </is>
-      </c>
-      <c r="G7" s="13" t="inlineStr">
-        <is>
-          <t>Руководитель + ИБ</t>
-        </is>
-      </c>
-      <c r="H7" s="13" t="inlineStr">
-        <is>
-          <t>не установлен</t>
-        </is>
-      </c>
-      <c r="I7" s="13" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="10" t="inlineStr">
+        <is>
+          <t>ADR-004</t>
+        </is>
+      </c>
+      <c r="B8" s="10" t="inlineStr">
+        <is>
+          <t>Архитектура</t>
+        </is>
+      </c>
+      <c r="C8" s="10" t="inlineStr">
+        <is>
+          <t>Классификация записи №1 (Матрица стейкхолдеров)</t>
+        </is>
+      </c>
+      <c r="D8" s="10" t="inlineStr">
+        <is>
+          <t>Заметка / нормативный документ / структурированный рабочий артефакт</t>
+        </is>
+      </c>
+      <c r="E8" s="10" t="inlineStr">
+        <is>
+          <t>Структурированный рабочий артефакт с будущим переносом в сущности стейкхолдеров</t>
+        </is>
+      </c>
+      <c r="F8" s="10" t="inlineStr">
+        <is>
+          <t>Требует отдельного проектирования структуры данных</t>
+        </is>
+      </c>
+      <c r="G8" s="10" t="inlineStr">
+        <is>
+          <t>Низкий</t>
+        </is>
+      </c>
+      <c r="H8" s="10" t="inlineStr">
+        <is>
+          <t>Архитектор</t>
+        </is>
+      </c>
+      <c r="I8" s="10" t="inlineStr">
         <is>
           <t>не принято</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="13" t="inlineStr">
-        <is>
-          <t>ADR-004</t>
-        </is>
-      </c>
-      <c r="B8" s="13" t="inlineStr">
-        <is>
-          <t>Модель хранения оригиналов документов</t>
-        </is>
-      </c>
-      <c r="C8" s="13" t="inlineStr">
-        <is>
-          <t>exec_source_document как единая точка входа / оставить exec_knowledge как есть</t>
-        </is>
-      </c>
-      <c r="D8" s="13" t="inlineStr">
-        <is>
-          <t>Единая точка входа exec_source_document, exec_knowledge переводится в legacy без удаления</t>
-        </is>
-      </c>
-      <c r="E8" s="13" t="inlineStr">
-        <is>
-          <t>Требует миграции 6 записей и доработки exec-planner-ai</t>
-        </is>
-      </c>
-      <c r="F8" s="13" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>ADR-005</t>
+        </is>
+      </c>
+      <c r="B9" s="10" t="inlineStr">
+        <is>
+          <t>Архитектура</t>
+        </is>
+      </c>
+      <c r="C9" s="10" t="inlineStr">
+        <is>
+          <t>Делегирование роли 'Утверждающий' в RBAC</t>
+        </is>
+      </c>
+      <c r="D9" s="10" t="inlineStr">
+        <is>
+          <t>Простая передача флага / делегирование с усиленным подтверждением</t>
+        </is>
+      </c>
+      <c r="E9" s="10" t="inlineStr">
+        <is>
+          <t>Только с усиленным подтверждением (повторный ввод / второй фактор)</t>
+        </is>
+      </c>
+      <c r="F9" s="10" t="inlineStr">
+        <is>
+          <t>Повышает трудоёмкость передачи роли, снижает риск компрометации</t>
+        </is>
+      </c>
+      <c r="G9" s="10" t="inlineStr">
         <is>
           <t>Средний</t>
         </is>
       </c>
-      <c r="G8" s="13" t="inlineStr">
-        <is>
-          <t>Архитектор/руководитель</t>
-        </is>
-      </c>
-      <c r="H8" s="13" t="inlineStr">
-        <is>
-          <t>не установлен</t>
-        </is>
-      </c>
-      <c r="I8" s="13" t="inlineStr">
+      <c r="H9" s="10" t="inlineStr">
+        <is>
+          <t>Архитектор/ИБ</t>
+        </is>
+      </c>
+      <c r="I9" s="10" t="inlineStr">
         <is>
           <t>не принято</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="13" t="inlineStr">
-        <is>
-          <t>ADR-005</t>
-        </is>
-      </c>
-      <c r="B9" s="13" t="inlineStr">
-        <is>
-          <t>Правила shadow-режима перед переключением RAG-источника</t>
-        </is>
-      </c>
-      <c r="C9" s="13" t="inlineStr">
-        <is>
-          <t>Переключить сразу / вести теневую выборку заданный период</t>
-        </is>
-      </c>
-      <c r="D9" s="13" t="inlineStr">
-        <is>
-          <t>Shadow-период не менее 2 недель, сравнение состава контекста, релевантности, качества цитат</t>
-        </is>
-      </c>
-      <c r="E9" s="13" t="inlineStr">
-        <is>
-          <t>Отсрочка перехода в canonical на срок shadow-периода</t>
-        </is>
-      </c>
-      <c r="F9" s="13" t="inlineStr">
-        <is>
-          <t>Низкий</t>
-        </is>
-      </c>
-      <c r="G9" s="13" t="inlineStr">
-        <is>
-          <t>Разработчик</t>
-        </is>
-      </c>
-      <c r="H9" s="13" t="inlineStr">
-        <is>
-          <t>не установлен</t>
-        </is>
-      </c>
-      <c r="I9" s="13" t="inlineStr">
-        <is>
-          <t>не принято</t>
-        </is>
-      </c>
-    </row>
     <row r="10">
-      <c r="A10" s="13" t="inlineStr">
+      <c r="A10" s="10" t="inlineStr">
         <is>
           <t>ADR-006</t>
         </is>
       </c>
-      <c r="B10" s="13" t="inlineStr">
-        <is>
-          <t>Постраничная разметка legacy-записей без установленных страниц</t>
-        </is>
-      </c>
-      <c r="C10" s="13" t="inlineStr">
-        <is>
-          <t>Создать виртуальную страницу 1 / оставить page_number=NULL с locator_type</t>
-        </is>
-      </c>
-      <c r="D10" s="13" t="inlineStr">
-        <is>
-          <t>page_number=NULL, locator_type=legacy_text_offset, UI показывает 'страница не установлена'</t>
-        </is>
-      </c>
-      <c r="E10" s="13" t="inlineStr">
-        <is>
-          <t>Ответы ИИ не будут содержать ложных ссылок на страницу</t>
-        </is>
-      </c>
-      <c r="F10" s="13" t="inlineStr">
-        <is>
-          <t>Высокий (при неверном выборе)</t>
-        </is>
-      </c>
-      <c r="G10" s="13" t="inlineStr">
-        <is>
-          <t>Архитектор</t>
-        </is>
-      </c>
-      <c r="H10" s="13" t="inlineStr">
-        <is>
-          <t>не установлен</t>
-        </is>
-      </c>
-      <c r="I10" s="13" t="inlineStr">
-        <is>
-          <t>не принято</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="13" t="inlineStr">
-        <is>
-          <t>ADR-007</t>
-        </is>
-      </c>
-      <c r="B11" s="13" t="inlineStr">
-        <is>
-          <t>Классификация записи №1 (Матрица стейкхолдеров)</t>
-        </is>
-      </c>
-      <c r="C11" s="13" t="inlineStr">
-        <is>
-          <t>Обычная заметка / нормативный документ / структурированный рабочий артефакт</t>
-        </is>
-      </c>
-      <c r="D11" s="13" t="inlineStr">
-        <is>
-          <t>Структурированный рабочий артефакт с будущим переносом элементов в сущности стейкхолдеров</t>
-        </is>
-      </c>
-      <c r="E11" s="13" t="inlineStr">
-        <is>
-          <t>Требует отдельного проектирования структуры данных стейкхолдеров</t>
-        </is>
-      </c>
-      <c r="F11" s="13" t="inlineStr">
-        <is>
-          <t>Низкий</t>
-        </is>
-      </c>
-      <c r="G11" s="13" t="inlineStr">
-        <is>
-          <t>Архитектор</t>
-        </is>
-      </c>
-      <c r="H11" s="13" t="inlineStr">
-        <is>
-          <t>не установлен</t>
-        </is>
-      </c>
-      <c r="I11" s="13" t="inlineStr">
-        <is>
-          <t>не принято</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="14" t="inlineStr">
-        <is>
-          <t>ADR-008</t>
-        </is>
-      </c>
-      <c r="B12" s="14" t="inlineStr">
-        <is>
-          <t>Происхождение 145 записей dept_functions (ДФМ)</t>
-        </is>
-      </c>
-      <c r="C12" s="14" t="inlineStr">
-        <is>
-          <t>Продолжить исследование сейчас / приостановить до появления первоисточника</t>
-        </is>
-      </c>
-      <c r="D12" s="14" t="inlineStr">
-        <is>
-          <t>Приостановлено по решению руководителя; статус 'не установлено' зафиксирован</t>
-        </is>
-      </c>
-      <c r="E12" s="14" t="inlineStr">
-        <is>
-          <t>Карточка Положения о ДФМ не создаётся до появления файла-источника</t>
-        </is>
-      </c>
-      <c r="F12" s="14" t="inlineStr">
-        <is>
-          <t>Низкий (заморожено)</t>
-        </is>
-      </c>
-      <c r="G12" s="14" t="inlineStr">
-        <is>
-          <t>Руководитель</t>
-        </is>
-      </c>
-      <c r="H12" s="14" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="I12" s="14" t="inlineStr">
-        <is>
-          <t>принято: приостановить</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="13" t="inlineStr">
-        <is>
-          <t>ADR-009</t>
-        </is>
-      </c>
-      <c r="B13" s="13" t="inlineStr">
-        <is>
-          <t>Природа счётчика облачных функций (191/200)</t>
-        </is>
-      </c>
-      <c r="C13" s="13" t="inlineStr">
-        <is>
-          <t>Считать гипотезой до скриншота / действовать по предположению</t>
-        </is>
-      </c>
-      <c r="D13" s="13" t="inlineStr">
-        <is>
-          <t>Считать гипотезой; функции не объединять и не удалять до подтверждения</t>
-        </is>
-      </c>
-      <c r="E13" s="13" t="inlineStr">
-        <is>
-          <t>Риск объединения работающих функций по ошибочному предположению снят</t>
-        </is>
-      </c>
-      <c r="F13" s="13" t="inlineStr">
-        <is>
-          <t>Низкий</t>
-        </is>
-      </c>
-      <c r="G13" s="13" t="inlineStr">
-        <is>
-          <t>Руководитель</t>
-        </is>
-      </c>
-      <c r="H13" s="13" t="inlineStr">
-        <is>
-          <t>не установлен</t>
-        </is>
-      </c>
-      <c r="I13" s="13" t="inlineStr">
-        <is>
-          <t>не принято — ожидается скриншот</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="13" t="inlineStr">
-        <is>
-          <t>ADR-010</t>
-        </is>
-      </c>
-      <c r="B14" s="13" t="inlineStr">
-        <is>
-          <t>Делегирование роли 'Утверждающий' в RBAC</t>
-        </is>
-      </c>
-      <c r="C14" s="13" t="inlineStr">
-        <is>
-          <t>Простая передача флага / делегирование с усиленным подтверждением</t>
-        </is>
-      </c>
-      <c r="D14" s="13" t="inlineStr">
-        <is>
-          <t>Делегирование только с усиленным подтверждением (повторный ввод / второй фактор)</t>
-        </is>
-      </c>
-      <c r="E14" s="13" t="inlineStr">
-        <is>
-          <t>Повышает трудоёмкость передачи роли, снижает риск компрометации</t>
-        </is>
-      </c>
-      <c r="F14" s="13" t="inlineStr">
-        <is>
-          <t>Средний (при отсутствии контроля)</t>
-        </is>
-      </c>
-      <c r="G14" s="13" t="inlineStr">
+      <c r="B10" s="10" t="inlineStr">
+        <is>
+          <t>Архитектура</t>
+        </is>
+      </c>
+      <c r="C10" s="10" t="inlineStr">
+        <is>
+          <t>Механизм фильтрации документов перед передачей AI-провайдеру</t>
+        </is>
+      </c>
+      <c r="D10" s="10" t="inlineStr">
+        <is>
+          <t>Фильтр по use_in_ai (текущий, недостаточный) / добавить confidentiality-фильтр на уровне SQL-запроса pick_knowledge</t>
+        </is>
+      </c>
+      <c r="E10" s="10" t="inlineStr">
+        <is>
+          <t>Добавить обязательный confidentiality-фильтр в pick_knowledge, не полагаться только на use_in_ai</t>
+        </is>
+      </c>
+      <c r="F10" s="10" t="inlineStr">
+        <is>
+          <t>Требует доработки exec-planner-ai и схемы exec_knowledge</t>
+        </is>
+      </c>
+      <c r="G10" s="10" t="inlineStr">
+        <is>
+          <t>Критический — влияет на RR-001</t>
+        </is>
+      </c>
+      <c r="H10" s="10" t="inlineStr">
         <is>
           <t>Архитектор/ИБ</t>
         </is>
       </c>
-      <c r="H14" s="13" t="inlineStr">
-        <is>
-          <t>не установлен</t>
-        </is>
-      </c>
-      <c r="I14" s="13" t="inlineStr">
+      <c r="I10" s="10" t="inlineStr">
         <is>
           <t>не принято</t>
         </is>
@@ -1607,7 +1286,1014 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B20"/>
+  <dimension ref="A1:G7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="42" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>Журнал управленческих решений</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="8" t="inlineStr">
+        <is>
+          <t>Решения об объёме, приоритетах и организации работы — не архитектурные решения</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="9" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B4" s="9" t="inlineStr">
+        <is>
+          <t>Дата</t>
+        </is>
+      </c>
+      <c r="C4" s="9" t="inlineStr">
+        <is>
+          <t>Решение</t>
+        </is>
+      </c>
+      <c r="D4" s="9" t="inlineStr">
+        <is>
+          <t>Обоснование / влияние</t>
+        </is>
+      </c>
+      <c r="E4" s="9" t="inlineStr">
+        <is>
+          <t>Владелец</t>
+        </is>
+      </c>
+      <c r="F4" s="9" t="inlineStr">
+        <is>
+          <t>Статус</t>
+        </is>
+      </c>
+      <c r="G4" s="9" t="inlineStr">
+        <is>
+          <t>Комментарий</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="13" t="inlineStr">
+        <is>
+          <t>DL-001</t>
+        </is>
+      </c>
+      <c r="B5" s="13" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="C5" s="13" t="inlineStr">
+        <is>
+          <t>Приостановить исследование происхождения 145 записей dept_functions (ДФМ)</t>
+        </is>
+      </c>
+      <c r="D5" s="13" t="inlineStr">
+        <is>
+          <t>Не влияет на архитектуру платформы; ограничивает объём текущего анализа</t>
+        </is>
+      </c>
+      <c r="E5" s="13" t="inlineStr">
+        <is>
+          <t>Руководитель</t>
+        </is>
+      </c>
+      <c r="F5" s="13" t="inlineStr">
+        <is>
+          <t>Принято</t>
+        </is>
+      </c>
+      <c r="G5" s="13" t="inlineStr">
+        <is>
+          <t>Решение зафиксировано в переписке 11.09.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="13" t="inlineStr">
+        <is>
+          <t>DL-002</t>
+        </is>
+      </c>
+      <c r="B6" s="13" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="C6" s="13" t="inlineStr">
+        <is>
+          <t>Не переходить к ТЗ и оценке трудозатрат без отдельной команды руководителя</t>
+        </is>
+      </c>
+      <c r="D6" s="13" t="inlineStr">
+        <is>
+          <t>Пакет проектирования готовится поэтапно, с раундами проверки</t>
+        </is>
+      </c>
+      <c r="E6" s="13" t="inlineStr">
+        <is>
+          <t>Руководитель</t>
+        </is>
+      </c>
+      <c r="F6" s="13" t="inlineStr">
+        <is>
+          <t>Принято</t>
+        </is>
+      </c>
+      <c r="G6" s="13" t="inlineStr">
+        <is>
+          <t>Действует на всех этапах проектирования</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="13" t="inlineStr">
+        <is>
+          <t>DL-003</t>
+        </is>
+      </c>
+      <c r="B7" s="13" t="inlineStr">
+        <is>
+          <t>не установлена</t>
+        </is>
+      </c>
+      <c r="C7" s="13" t="inlineStr">
+        <is>
+          <t>Использование YandexGPT для внутренних нормативных документов Банка</t>
+        </is>
+      </c>
+      <c r="D7" s="13" t="inlineStr">
+        <is>
+          <t>КРИТИЧНО: до решения все 6 записей exec_knowledge технически доступны AI-провайдеру</t>
+        </is>
+      </c>
+      <c r="E7" s="13" t="inlineStr">
+        <is>
+          <t>Руководитель + ИБ</t>
+        </is>
+      </c>
+      <c r="F7" s="13" t="inlineStr">
+        <is>
+          <t>Требуется решение</t>
+        </is>
+      </c>
+      <c r="G7" s="13" t="inlineStr">
+        <is>
+          <t>См. Risk Register RR-001, рекомендация — временно снять use_in_ai</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A1:G1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="55" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="55" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>Read-only аудит фактического маршрута данных в AI-провайдера</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="8" t="inlineStr">
+        <is>
+          <t>Выполнено 11.09.2026: чтение кода, схемы БД, списка секретов, логов. Тестовые запросы НЕ отправлялись</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="9" t="inlineStr">
+        <is>
+          <t>Параметр</t>
+        </is>
+      </c>
+      <c r="B4" s="9" t="inlineStr">
+        <is>
+          <t>Установленное значение</t>
+        </is>
+      </c>
+      <c r="C4" s="9" t="inlineStr">
+        <is>
+          <t>Статус</t>
+        </is>
+      </c>
+      <c r="D4" s="9" t="inlineStr">
+        <is>
+          <t>Источник / комментарий</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="13" t="inlineStr">
+        <is>
+          <t>AI-провайдер</t>
+        </is>
+      </c>
+      <c r="B5" s="13" t="inlineStr">
+        <is>
+          <t>YandexGPT (Yandex Cloud)</t>
+        </is>
+      </c>
+      <c r="C5" s="11" t="inlineStr">
+        <is>
+          <t>подтверждено кодом</t>
+        </is>
+      </c>
+      <c r="D5" s="13" t="inlineStr">
+        <is>
+          <t>backend/exec-planner-ai/index.py, строка GPT_URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="13" t="inlineStr">
+        <is>
+          <t>Endpoint</t>
+        </is>
+      </c>
+      <c r="B6" s="13" t="inlineStr">
+        <is>
+          <t>https://llm.api.cloud.yandex.net/foundationModels/v1/completion</t>
+        </is>
+      </c>
+      <c r="C6" s="11" t="inlineStr">
+        <is>
+          <t>подтверждено кодом</t>
+        </is>
+      </c>
+      <c r="D6" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="13" t="inlineStr">
+        <is>
+          <t>Модель</t>
+        </is>
+      </c>
+      <c r="B7" s="13" t="inlineStr">
+        <is>
+          <t>yandexgpt/latest (через modelUri gpt://{FOLDER_ID}/yandexgpt/latest)</t>
+        </is>
+      </c>
+      <c r="C7" s="11" t="inlineStr">
+        <is>
+          <t>подтверждено кодом</t>
+        </is>
+      </c>
+      <c r="D7" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="13" t="inlineStr">
+        <is>
+          <t>Тариф / договорные условия</t>
+        </is>
+      </c>
+      <c r="B8" s="13" t="inlineStr">
+        <is>
+          <t>не установлено</t>
+        </is>
+      </c>
+      <c r="C8" s="10" t="inlineStr">
+        <is>
+          <t>требует проверки</t>
+        </is>
+      </c>
+      <c r="D8" s="13" t="inlineStr">
+        <is>
+          <t>Не входит в зону технического аудита кода — нужен запрос к владельцу облачного аккаунта</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="13" t="inlineStr">
+        <is>
+          <t>Способ авторизации</t>
+        </is>
+      </c>
+      <c r="B9" s="13" t="inlineStr">
+        <is>
+          <t>Api-Key через заголовок Authorization</t>
+        </is>
+      </c>
+      <c r="C9" s="11" t="inlineStr">
+        <is>
+          <t>подтверждено кодом</t>
+        </is>
+      </c>
+      <c r="D9" s="13" t="inlineStr">
+        <is>
+          <t>Ключ хранится в секрете YANDEX_GPT_API_KEY, значение не просматривалось</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="13" t="inlineStr">
+        <is>
+          <t>Что включается в payload</t>
+        </is>
+      </c>
+      <c r="B10" s="13" t="inlineStr">
+        <is>
+          <t>System-промпт + полный текст релевантных чанков exec_knowledge (до 7000 символов, до 8 фрагментов)</t>
+        </is>
+      </c>
+      <c r="C10" s="11" t="inlineStr">
+        <is>
+          <t>подтверждено кодом</t>
+        </is>
+      </c>
+      <c r="D10" s="13" t="inlineStr">
+        <is>
+          <t>Функция pick_knowledge, строки 122-194</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="13" t="inlineStr">
+        <is>
+          <t>Передаётся полный текст или фрагмент</t>
+        </is>
+      </c>
+      <c r="B11" s="13" t="inlineStr">
+        <is>
+          <t>Полный текст чанка (content.strip()), НЕ урезанный</t>
+        </is>
+      </c>
+      <c r="C11" s="11" t="inlineStr">
+        <is>
+          <t>подтверждено кодом</t>
+        </is>
+      </c>
+      <c r="D11" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="13" t="inlineStr">
+        <is>
+          <t>Фильтрация по use_in_ai</t>
+        </is>
+      </c>
+      <c r="B12" s="13" t="inlineStr">
+        <is>
+          <t>Да, WHERE use_in_ai=true AND status='active'</t>
+        </is>
+      </c>
+      <c r="C12" s="11" t="inlineStr">
+        <is>
+          <t>подтверждено кодом</t>
+        </is>
+      </c>
+      <c r="D12" s="13" t="inlineStr">
+        <is>
+          <t>НО: все 6 записей имеют use_in_ai=true — фильтр не исключает ничего фактически</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="13" t="inlineStr">
+        <is>
+          <t>Фильтрация по конфиденциальности</t>
+        </is>
+      </c>
+      <c r="B13" s="13" t="inlineStr">
+        <is>
+          <t>ОТСУТСТВУЕТ</t>
+        </is>
+      </c>
+      <c r="C13" s="12" t="inlineStr">
+        <is>
+          <t>не обнаружено</t>
+        </is>
+      </c>
+      <c r="D13" s="13" t="inlineStr">
+        <is>
+          <t>Поля confidentiality в схеме exec_knowledge нет вовсе</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="13" t="inlineStr">
+        <is>
+          <t>Журнал предыдущих запросов к AI</t>
+        </is>
+      </c>
+      <c r="B14" s="13" t="inlineStr">
+        <is>
+          <t>ОТСУТСТВУЕТ</t>
+        </is>
+      </c>
+      <c r="C14" s="12" t="inlineStr">
+        <is>
+          <t>не обнаружено</t>
+        </is>
+      </c>
+      <c r="D14" s="13" t="inlineStr">
+        <is>
+          <t>Нет ни таблицы в БД, ни logger/print. get_logs по backend/exec-planner-ai вернул 0 записей</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="13" t="inlineStr">
+        <is>
+          <t>Возможность установить, что уже передавалось</t>
+        </is>
+      </c>
+      <c r="B15" s="13" t="inlineStr">
+        <is>
+          <t>НЕВОЗМОЖНО</t>
+        </is>
+      </c>
+      <c r="C15" s="13" t="inlineStr">
+        <is>
+          <t>установленный факт отсутствия данных</t>
+        </is>
+      </c>
+      <c r="D15" s="13" t="inlineStr">
+        <is>
+          <t>Без журнала нельзя технически подтвердить или опровергнуть прошлые передачи документа №6</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="13" t="inlineStr">
+        <is>
+          <t>Срок хранения запросов провайдером</t>
+        </is>
+      </c>
+      <c r="B16" s="13" t="inlineStr">
+        <is>
+          <t>не установлено</t>
+        </is>
+      </c>
+      <c r="C16" s="10" t="inlineStr">
+        <is>
+          <t>требует проверки</t>
+        </is>
+      </c>
+      <c r="D16" s="13" t="inlineStr">
+        <is>
+          <t>вне зоны технического аудита кода</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="13" t="inlineStr">
+        <is>
+          <t>Использование данных для обучения модели провайдером</t>
+        </is>
+      </c>
+      <c r="B17" s="13" t="inlineStr">
+        <is>
+          <t>не установлено</t>
+        </is>
+      </c>
+      <c r="C17" s="12" t="inlineStr">
+        <is>
+          <t>требует проверки — БЛОКИРУЮЩИЙ</t>
+        </is>
+      </c>
+      <c r="D17" s="13" t="inlineStr">
+        <is>
+          <t>см. Risk Register RR-001</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="13" t="inlineStr">
+        <is>
+          <t>Регион обработки данных</t>
+        </is>
+      </c>
+      <c r="B18" s="13" t="inlineStr">
+        <is>
+          <t>не установлено</t>
+        </is>
+      </c>
+      <c r="C18" s="10" t="inlineStr">
+        <is>
+          <t>требует проверки</t>
+        </is>
+      </c>
+      <c r="D18" s="13" t="inlineStr">
+        <is>
+          <t>вне зоны технического аудита кода</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="13" t="inlineStr">
+        <is>
+          <t>Субпроцессоры</t>
+        </is>
+      </c>
+      <c r="B19" s="13" t="inlineStr">
+        <is>
+          <t>не установлено</t>
+        </is>
+      </c>
+      <c r="C19" s="10" t="inlineStr">
+        <is>
+          <t>требует проверки</t>
+        </is>
+      </c>
+      <c r="D19" s="13" t="inlineStr">
+        <is>
+          <t>вне зоны технического аудита кода</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="13" t="inlineStr">
+        <is>
+          <t>Тестовая отправка ВНД во внешний AI в рамках этого аудита</t>
+        </is>
+      </c>
+      <c r="B20" s="13" t="inlineStr">
+        <is>
+          <t>НЕ ВЫПОЛНЯЛАСЬ</t>
+        </is>
+      </c>
+      <c r="C20" s="13" t="inlineStr">
+        <is>
+          <t>по прямому указанию руководителя</t>
+        </is>
+      </c>
+      <c r="D20" s="13" t="inlineStr">
+        <is>
+          <t>Аудит строго read-only: чтение кода, схемы БД, списка секретов и логов</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A2:D2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="55" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="50" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>Реестр открытых вопросов</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="8" t="inlineStr">
+        <is>
+          <t>Вопросы, не являющиеся ни архитектурным, ни управленческим решением сами по себе</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="9" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B4" s="9" t="inlineStr">
+        <is>
+          <t>Вопрос</t>
+        </is>
+      </c>
+      <c r="C4" s="9" t="inlineStr">
+        <is>
+          <t>Статус</t>
+        </is>
+      </c>
+      <c r="D4" s="9" t="inlineStr">
+        <is>
+          <t>Владелец</t>
+        </is>
+      </c>
+      <c r="E4" s="9" t="inlineStr">
+        <is>
+          <t>Комментарий</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="13" t="inlineStr">
+        <is>
+          <t>ISS-001</t>
+        </is>
+      </c>
+      <c r="B5" s="13" t="inlineStr">
+        <is>
+          <t>Заголовок записи №5 содержит непроверенное слово 'официальный'</t>
+        </is>
+      </c>
+      <c r="C5" s="13" t="inlineStr">
+        <is>
+          <t>Открыт</t>
+        </is>
+      </c>
+      <c r="D5" s="13" t="inlineStr">
+        <is>
+          <t>Владелец документа</t>
+        </is>
+      </c>
+      <c r="E5" s="13" t="inlineStr">
+        <is>
+          <t>Развести original_title/display_title — см. ADR (было ADR-002 в v1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="13" t="inlineStr">
+        <is>
+          <t>ISS-002</t>
+        </is>
+      </c>
+      <c r="B6" s="13" t="inlineStr">
+        <is>
+          <t>Природа счётчика облачных функций 191/200 не установлена</t>
+        </is>
+      </c>
+      <c r="C6" s="13" t="inlineStr">
+        <is>
+          <t>Открыт</t>
+        </is>
+      </c>
+      <c r="D6" s="13" t="inlineStr">
+        <is>
+          <t>Руководитель</t>
+        </is>
+      </c>
+      <c r="E6" s="13" t="inlineStr">
+        <is>
+          <t>Ожидается скриншот; функции не объединять и не удалять до подтверждения</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="13" t="inlineStr">
+        <is>
+          <t>ISS-003</t>
+        </is>
+      </c>
+      <c r="B7" s="13" t="inlineStr">
+        <is>
+          <t>get_logs не хранит историю дольше короткого периода — невозможен ретроспективный аудит</t>
+        </is>
+      </c>
+      <c r="C7" s="13" t="inlineStr">
+        <is>
+          <t>Открыт</t>
+        </is>
+      </c>
+      <c r="D7" s="13" t="inlineStr">
+        <is>
+          <t>Разработчик</t>
+        </is>
+      </c>
+      <c r="E7" s="13" t="inlineStr">
+        <is>
+          <t>Технологическое ограничение платформы, не специфично для этого пакета</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="13" t="inlineStr">
+        <is>
+          <t>ISS-004</t>
+        </is>
+      </c>
+      <c r="B8" s="13" t="inlineStr">
+        <is>
+          <t>Mermaid-файлы не проверены автокомпиляцией (mermaid-cli недоступен в песочнице)</t>
+        </is>
+      </c>
+      <c r="C8" s="13" t="inlineStr">
+        <is>
+          <t>Открыт</t>
+        </is>
+      </c>
+      <c r="D8" s="13" t="inlineStr">
+        <is>
+          <t>Разработчик</t>
+        </is>
+      </c>
+      <c r="E8" s="13" t="inlineStr">
+        <is>
+          <t>Рекомендуется ручная проверка на mermaid.live перед утверждением пакета</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="55" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>Реестр рисков с владельцами</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="8" t="inlineStr">
+        <is>
+          <t>RR-001 — критический, блокирующий; требует решения до дальнейшего расширения базы знаний</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="9" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B4" s="9" t="inlineStr">
+        <is>
+          <t>Риск</t>
+        </is>
+      </c>
+      <c r="C4" s="9" t="inlineStr">
+        <is>
+          <t>Уровень</t>
+        </is>
+      </c>
+      <c r="D4" s="9" t="inlineStr">
+        <is>
+          <t>Затронутые объекты</t>
+        </is>
+      </c>
+      <c r="E4" s="9" t="inlineStr">
+        <is>
+          <t>Владелец риска</t>
+        </is>
+      </c>
+      <c r="F4" s="9" t="inlineStr">
+        <is>
+          <t>Предлагаемая мера</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="13" t="inlineStr">
+        <is>
+          <t>RR-001</t>
+        </is>
+      </c>
+      <c r="B5" s="13" t="inlineStr">
+        <is>
+          <t>Внутренние документы Банка технически доступны внешнему AI-провайдеру (YandexGPT) без ограничения по конфиденциальности</t>
+        </is>
+      </c>
+      <c r="C5" s="12" t="inlineStr">
+        <is>
+          <t>Критический</t>
+        </is>
+      </c>
+      <c r="D5" s="13" t="inlineStr">
+        <is>
+          <t>Все 6 записей exec_knowledge, включая реальный ВНД (№6)</t>
+        </is>
+      </c>
+      <c r="E5" s="13" t="inlineStr">
+        <is>
+          <t>Руководитель + ИБ</t>
+        </is>
+      </c>
+      <c r="F5" s="13" t="inlineStr">
+        <is>
+          <t>Временно снять use_in_ai с №6 вручную; реализовать confidentiality-фильтр (ADR-006); получить ответ провайдера по обучению на данных (лист 11)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="13" t="inlineStr">
+        <is>
+          <t>RR-002</t>
+        </is>
+      </c>
+      <c r="B6" s="13" t="inlineStr">
+        <is>
+          <t>Нет журнала запросов к AI-провайдеру — невозможно расследование постфактум</t>
+        </is>
+      </c>
+      <c r="C6" s="12" t="inlineStr">
+        <is>
+          <t>Высокий</t>
+        </is>
+      </c>
+      <c r="D6" s="13" t="inlineStr">
+        <is>
+          <t>exec-planner-ai</t>
+        </is>
+      </c>
+      <c r="E6" s="13" t="inlineStr">
+        <is>
+          <t>Разработчик</t>
+        </is>
+      </c>
+      <c r="F6" s="13" t="inlineStr">
+        <is>
+          <t>Добавить журналирование запросов (что передано, когда, кем инициировано) до расширения использования</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="13" t="inlineStr">
+        <is>
+          <t>RR-003</t>
+        </is>
+      </c>
+      <c r="B7" s="13" t="inlineStr">
+        <is>
+          <t>Отсутствие статуса верификации у 5 из 6 документов при активном использовании в AI-контексте</t>
+        </is>
+      </c>
+      <c r="C7" s="12" t="inlineStr">
+        <is>
+          <t>Высокий</t>
+        </is>
+      </c>
+      <c r="D7" s="13" t="inlineStr">
+        <is>
+          <t>exec_knowledge</t>
+        </is>
+      </c>
+      <c r="E7" s="13" t="inlineStr">
+        <is>
+          <t>Владелец документа</t>
+        </is>
+      </c>
+      <c r="F7" s="13" t="inlineStr">
+        <is>
+          <t>Провести верификацию или снять use_in_ai до её завершения</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="13" t="inlineStr">
+        <is>
+          <t>RR-004</t>
+        </is>
+      </c>
+      <c r="B8" s="13" t="inlineStr">
+        <is>
+          <t>145 записей dept_functions содержат непроверенные дубли и не привязаны к первоисточнику</t>
+        </is>
+      </c>
+      <c r="C8" s="10" t="inlineStr">
+        <is>
+          <t>Средний (заморожен по DL-001)</t>
+        </is>
+      </c>
+      <c r="D8" s="13" t="inlineStr">
+        <is>
+          <t>dept_functions</t>
+        </is>
+      </c>
+      <c r="E8" s="13" t="inlineStr">
+        <is>
+          <t>Руководитель</t>
+        </is>
+      </c>
+      <c r="F8" s="13" t="inlineStr">
+        <is>
+          <t>Возврат к вопросу после появления первоисточника Положения о ДФМ</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="13" t="inlineStr">
+        <is>
+          <t>RR-005</t>
+        </is>
+      </c>
+      <c r="B9" s="13" t="inlineStr">
+        <is>
+          <t>Коды 81.42 и 81.342 используются в exec_center_function, но отсутствуют в справочнике</t>
+        </is>
+      </c>
+      <c r="C9" s="10" t="inlineStr">
+        <is>
+          <t>Средний</t>
+        </is>
+      </c>
+      <c r="D9" s="13" t="inlineStr">
+        <is>
+          <t>exec_center_function, bank_function_catalog</t>
+        </is>
+      </c>
+      <c r="E9" s="13" t="inlineStr">
+        <is>
+          <t>Владелец данных</t>
+        </is>
+      </c>
+      <c r="F9" s="13" t="inlineStr">
+        <is>
+          <t>Исправить сопоставление после решения по ADR о структуре справочника (см. предыдущие раунды пакета)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1615,218 +2301,242 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="10" t="inlineStr">
+      <c r="A1" s="7" t="inlineStr">
         <is>
           <t>Границы первого этапа реализации</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="11" t="inlineStr">
-        <is>
-          <t>Формируется до оценки трудозатрат, чтобы оценка не была завышенной или размытой</t>
+      <c r="A2" s="8" t="inlineStr">
+        <is>
+          <t>Confidentiality-фильтр и журналирование AI-запросов добавлены как срочные пункты по факту аудита (лист 11)</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="12" t="inlineStr">
+      <c r="A4" s="9" t="inlineStr">
         <is>
           <t>Категория</t>
         </is>
       </c>
-      <c r="B4" s="12" t="inlineStr">
+      <c r="B4" s="9" t="inlineStr">
         <is>
           <t>Пункт</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="14" t="inlineStr">
+      <c r="A5" s="11" t="inlineStr">
         <is>
           <t>В границах этапа 1</t>
         </is>
       </c>
-      <c r="B5" s="14" t="inlineStr">
+      <c r="B5" s="11" t="inlineStr">
         <is>
           <t>Канонический реестр источников (exec_source_document)</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="14" t="inlineStr">
+      <c r="A6" s="11" t="inlineStr">
         <is>
           <t>В границах этапа 1</t>
         </is>
       </c>
-      <c r="B6" s="14" t="inlineStr">
+      <c r="B6" s="11" t="inlineStr">
         <is>
           <t>Редакции документов (document_revision)</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="14" t="inlineStr">
+      <c r="A7" s="11" t="inlineStr">
         <is>
           <t>В границах этапа 1</t>
         </is>
       </c>
-      <c r="B7" s="14" t="inlineStr">
+      <c r="B7" s="11" t="inlineStr">
         <is>
           <t>Файлы-оригиналы, привязка и проверка доступности</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="14" t="inlineStr">
+      <c r="A8" s="11" t="inlineStr">
         <is>
           <t>В границах этапа 1</t>
         </is>
       </c>
-      <c r="B8" s="14" t="inlineStr">
+      <c r="B8" s="11" t="inlineStr">
         <is>
           <t>Страницы и структурные пункты (там, где устанавливаются)</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="14" t="inlineStr">
+      <c r="A9" s="11" t="inlineStr">
         <is>
           <t>В границах этапа 1</t>
         </is>
       </c>
-      <c r="B9" s="14" t="inlineStr">
+      <c r="B9" s="11" t="inlineStr">
         <is>
           <t>Legacy-связи для 6 записей exec_knowledge, без удаления исходных данных</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="14" t="inlineStr">
+      <c r="A10" s="11" t="inlineStr">
         <is>
           <t>В границах этапа 1</t>
         </is>
       </c>
-      <c r="B10" s="14" t="inlineStr">
+      <c r="B10" s="11" t="inlineStr">
         <is>
           <t>Статусы происхождения и верификации для документов</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="14" t="inlineStr">
+      <c r="A11" s="11" t="inlineStr">
         <is>
           <t>В границах этапа 1</t>
         </is>
       </c>
-      <c r="B11" s="14" t="inlineStr">
-        <is>
-          <t>Базовый доступ к документам (каркас ролей, не полная RBAC-матрица)</t>
+      <c r="B11" s="11" t="inlineStr">
+        <is>
+          <t>Базовый доступ к документам (каркас ролей)</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="14" t="inlineStr">
+      <c r="A12" s="11" t="inlineStr">
         <is>
           <t>В границах этапа 1</t>
         </is>
       </c>
-      <c r="B12" s="14" t="inlineStr">
+      <c r="B12" s="11" t="inlineStr">
         <is>
           <t>Аудит операций с документами через API</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="14" t="inlineStr">
+      <c r="A13" s="11" t="inlineStr">
         <is>
           <t>В границах этапа 1</t>
         </is>
       </c>
-      <c r="B13" s="14" t="inlineStr">
+      <c r="B13" s="11" t="inlineStr">
         <is>
           <t>Shadow-режим для exec-planner-ai</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="14" t="inlineStr">
+      <c r="A14" s="11" t="inlineStr">
         <is>
           <t>В границах этапа 1</t>
         </is>
       </c>
-      <c r="B14" s="14" t="inlineStr">
+      <c r="B14" s="11" t="inlineStr">
         <is>
           <t>Миграция 6 legacy-записей без удаления</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="15" t="inlineStr">
+      <c r="A15" s="11" t="inlineStr">
+        <is>
+          <t>В границах этапа 1</t>
+        </is>
+      </c>
+      <c r="B15" s="11" t="inlineStr">
+        <is>
+          <t>Confidentiality-фильтр перед передачей в AI-провайдер (ADR-006, срочно по RR-001)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="11" t="inlineStr">
+        <is>
+          <t>В границах этапа 1</t>
+        </is>
+      </c>
+      <c r="B16" s="11" t="inlineStr">
+        <is>
+          <t>Журналирование запросов к AI-провайдеру (RR-002)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="12" t="inlineStr">
         <is>
           <t>НЕ в границах этапа 1</t>
         </is>
       </c>
-      <c r="B15" s="15" t="inlineStr">
+      <c r="B17" s="12" t="inlineStr">
         <is>
           <t>Полная очистка и дедупликация 145 записей ДФМ</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="15" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="12" t="inlineStr">
         <is>
           <t>НЕ в границах этапа 1</t>
         </is>
       </c>
-      <c r="B16" s="15" t="inlineStr">
+      <c r="B18" s="12" t="inlineStr">
         <is>
           <t>Перестройка всего портфеля (инициативы/проекты/поручения/эффекты)</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="15" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="12" t="inlineStr">
         <is>
           <t>НЕ в границах этапа 1</t>
         </is>
       </c>
-      <c r="B17" s="15" t="inlineStr">
+      <c r="B19" s="12" t="inlineStr">
         <is>
           <t>Статусная модель для всех ~20 затронутых таблиц</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="15" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="12" t="inlineStr">
         <is>
           <t>НЕ в границах этапа 1</t>
         </is>
       </c>
-      <c r="B18" s="15" t="inlineStr">
+      <c r="B20" s="12" t="inlineStr">
         <is>
           <t>Редизайн кабинета и дашборда</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="15" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="12" t="inlineStr">
         <is>
           <t>НЕ в границах этапа 1</t>
         </is>
       </c>
-      <c r="B19" s="15" t="inlineStr">
+      <c r="B21" s="12" t="inlineStr">
         <is>
           <t>Реорганизация облачных функций</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="15" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="12" t="inlineStr">
         <is>
           <t>НЕ в границах этапа 1</t>
         </is>
       </c>
-      <c r="B20" s="15" t="inlineStr">
+      <c r="B22" s="12" t="inlineStr">
         <is>
           <t>Автогенерация презентаций</t>
         </is>
@@ -1847,24 +2557,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A33"/>
+  <dimension ref="A1:A31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="7" t="inlineStr">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>Записка руководителю — кратко, без технических деталей</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr"/>
-    </row>
+    <row r="2"/>
     <row r="3">
-      <c r="A3" s="8" t="inlineStr">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>ЧТО ВЫЯВЛЕНО</t>
         </is>
@@ -1887,112 +2595,106 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Часть справочных кодов (2 из 14 сопоставлений с функциями Центра) оказались ошибочно придуманы</t>
+          <t>При проверке дополнительно установлено: система использует внешний сервис YandexGPT для помощи</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>на предыдущем шаге работы и не существуют в справочнике Банка — уже помечены к исправлению.</t>
+          <t>в планировании, и ВСЕ 6 документов сейчас технически доступны этому сервису без ограничений —</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr"/>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>включая внутренний нормативный документ Банка. Проверить, передавался ли он уже, невозможно —</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="8" t="inlineStr">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>система не ведёт журнал таких обращений.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10"/>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>ОСНОВНЫЕ РИСКИ</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>1. Непроверенный текст может восприниматься как официальный документ Банка (пример — заголовок</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   со словом 'официальный' у документа без подтверждённого оригинала).</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2. В модуле базы знаний нет разделения документов по уровню конфиденциальности и нет журнала,</t>
+          <t>1. Нет технического запрета на передачу внутренних документов Банка во внешний ИИ-сервис —</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">   кто и когда их читал. Компенсируется ли это на уровне всей платформы — требует отдельной проверки.</t>
+          <t xml:space="preserve">   это факт, не предположение. Требуется ваше решение: разрешить, ограничить или отключить.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>3. Не подтверждены условия работы внешнего ИИ-провайдера с внутренними документами Банка —</t>
+          <t>2. Непроверенный текст может восприниматься как официальный документ Банка.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">   вопрос блокирующий, до его решения новые внутренние документы загружать не рекомендуется.</t>
+          <t>3. В модуле базы знаний нет разделения документов по уровню конфиденциальности и нет журнала,</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="8" t="inlineStr">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   кто и когда их читал.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17"/>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
         <is>
           <t>ПРЕДЛАГАЕМАЯ ЦЕЛЕВАЯ МОДЕЛЬ</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Единая точка входа для всех документов с обязательным хранением оригинала, историей редакций</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>и четырьмя независимыми статусами (кто создал запись, проверена ли она, согласована ли,</t>
+          <t>Единая точка входа для всех документов с обязательным хранением оригинала, историей редакций</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>действует ли документ сейчас). Права на согласование и утверждение — только у человека,</t>
+          <t>и независимыми статусами. Права на согласование и утверждение — только у человека; сейчас это</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>искусственный интеллект может только предлагать.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr"/>
-    </row>
+          <t>тоже не техническое ограничение, а требование к будущей модели.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22"/>
     <row r="23">
-      <c r="A23" s="8" t="inlineStr">
+      <c r="A23" s="5" t="inlineStr">
         <is>
           <t>ЧТО ПРЕДЛАГАЕТСЯ РЕАЛИЗОВАТЬ ПЕРВЫМ ЭТАПОМ</t>
         </is>
@@ -2001,66 +2703,50 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Перевод 6 существующих документов в новую модель без потери данных, базовые статусы и права</t>
+          <t>Перевод 6 существующих документов в новую модель без потери данных, отключение use_in_ai у документов</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>доступа, тестовый режим для проверки качества ответов ИИ перед переключением на новую модель.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Массовую проверку 145 записей по ДФМ и перестройку остальных разделов кабинета — не включаем</t>
-        </is>
-      </c>
-    </row>
+          <t>с непроверенным статусом до вашего решения, добавление журнала обращений к YandexGPT.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26"/>
     <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>в первый этап, чтобы не размывать сроки и объём работ.</t>
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>КАКИЕ РЕШЕНИЯ ТРЕБУЮТСЯ ОТ ВАС — СРОЧНО</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr"/>
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>— разрешить ли использование YandexGPT для внутренних нормативных документов Банка (блокирующий,</t>
+        </is>
+      </c>
     </row>
     <row r="29">
-      <c r="A29" s="8" t="inlineStr">
-        <is>
-          <t>КАКИЕ РЕШЕНИЯ ТРЕБУЮТСЯ ОТ ВАС</t>
+      <c r="A29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  см. Risk Register RR-001) — до решения рекомендую вручную снять use_in_ai с документа №6;</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>— можно ли использовать внешний ИИ-сервис для работы с внутренними документами Банка (блокирующий);</t>
+          <t>— подтвердить состав первого этапа;</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>— подтвердить состав первого этапа (см. таблицу границ в пакете);</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>— по документу с неподтверждённым статусом ('официальный') — как отображать его в кабинете</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  до проверки первоисточника.</t>
+          <t>— по документу с заголовком 'официальный' — как отображать его до проверки первоисточника.</t>
         </is>
       </c>
     </row>
@@ -2075,7 +2761,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A17"/>
+  <dimension ref="A1:A21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="95" customWidth="1" min="1" max="1"/>
@@ -2091,7 +2777,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Версия: v1</t>
+          <t>Версия: v2</t>
         </is>
       </c>
     </row>
@@ -2103,7 +2789,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="9" t="inlineStr">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>Статус: Draft / На рассмотрении — НЕ утверждён, миграции НЕ выполнены</t>
         </is>
@@ -2119,7 +2805,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0. README — манифест, границы анализа, установленные факты и предположения, состав файлов</t>
+          <t>0. README — манифест, что изменилось с v1, установленные факты и предположения</t>
         </is>
       </c>
     </row>
@@ -2140,7 +2826,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>4. Таблица соответствия полей (исправленная)</t>
+          <t>4. Таблица соответствия полей</t>
         </is>
       </c>
     </row>
@@ -2161,7 +2847,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>7. Расширенная матрица RBAC</t>
+          <t>7. Расширенная матрица RBAC (целевая модель)</t>
         </is>
       </c>
     </row>
@@ -2175,14 +2861,42 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>9. ADR-реестр (10 архитектурных решений)</t>
+          <t>9. ADR-реестр — только архитектурные решения</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>10. Границы первого этапа реализации</t>
+          <t>10. Decision Log — управленческие решения</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>11. Аудит AI-маршрута (НОВОЕ в v2) — read-only, без тестовых запросов</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>12. Issue Register — открытые вопросы</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>13. Risk Register — риски с владельцами</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>14. Границы первого этапа реализации</t>
         </is>
       </c>
     </row>
@@ -2197,295 +2911,331 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="60" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="55" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="28" customWidth="1" min="7" max="7"/>
+    <col width="26" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="10" t="inlineStr">
+      <c r="A1" s="7" t="inlineStr">
         <is>
           <t>Решения по каждой из 6 legacy-записей exec_knowledge</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="11" t="inlineStr">
-        <is>
-          <t>Ни одна запись не получает статус «канонический документ» без подтверждённого и сверенного оригинала</t>
+      <c r="A2" s="8" t="inlineStr">
+        <is>
+          <t>Добавлен столбец 'Доступность AI-провайдеру' — новое в v2, по факту из аудита (лист 11)</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="12" t="inlineStr">
+      <c r="A4" s="9" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B4" s="12" t="inlineStr">
+      <c r="B4" s="9" t="inlineStr">
         <is>
           <t>Название</t>
         </is>
       </c>
-      <c r="C4" s="12" t="inlineStr">
+      <c r="C4" s="9" t="inlineStr">
         <is>
           <t>Целевая классификация</t>
         </is>
       </c>
-      <c r="D4" s="12" t="inlineStr">
+      <c r="D4" s="9" t="inlineStr">
         <is>
           <t>Обоснование / условия</t>
         </is>
       </c>
-      <c r="E4" s="12" t="inlineStr">
+      <c r="E4" s="9" t="inlineStr">
         <is>
           <t>Происхождение (предполагаемое)</t>
         </is>
       </c>
-      <c r="F4" s="12" t="inlineStr">
+      <c r="F4" s="9" t="inlineStr">
         <is>
           <t>Верификация</t>
         </is>
       </c>
-      <c r="G4" s="12" t="inlineStr">
+      <c r="G4" s="9" t="inlineStr">
         <is>
           <t>Доступность оригинала</t>
         </is>
       </c>
+      <c r="H4" s="9" t="inlineStr">
+        <is>
+          <t>Доступность AI-провайдеру</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="13" t="inlineStr">
+      <c r="A5" s="10" t="inlineStr">
         <is>
           <t>№1</t>
         </is>
       </c>
-      <c r="B5" s="13" t="inlineStr">
+      <c r="B5" s="10" t="inlineStr">
         <is>
           <t>Матрица стейкхолдеров по этапам инициативы</t>
         </is>
       </c>
-      <c r="C5" s="13" t="inlineStr">
+      <c r="C5" s="10" t="inlineStr">
         <is>
           <t>Структурированный рабочий артефакт</t>
         </is>
       </c>
-      <c r="D5" s="13" t="inlineStr">
-        <is>
-          <t>Не документ и не обычная заметка. В перспективе элементы переносятся в структурированные сущности (стейкхолдер, оргединица, роль, влияние, интерес, стратегия), с сохранением связи на исходную legacy-запись.</t>
-        </is>
-      </c>
-      <c r="E5" s="13" t="inlineStr">
+      <c r="D5" s="10" t="inlineStr">
+        <is>
+          <t>Не документ и не обычная заметка. В перспективе элементы переносятся в структурированные сущности, с сохранением связи на исходную legacy-запись.</t>
+        </is>
+      </c>
+      <c r="E5" s="10" t="inlineStr">
         <is>
           <t>не установлено</t>
         </is>
       </c>
-      <c r="F5" s="13" t="inlineStr">
+      <c r="F5" s="10" t="inlineStr">
         <is>
           <t>не проверено</t>
         </is>
       </c>
-      <c r="G5" s="13" t="inlineStr">
+      <c r="G5" s="10" t="inlineStr">
         <is>
           <t>не связан</t>
         </is>
       </c>
+      <c r="H5" s="10" t="inlineStr">
+        <is>
+          <t>true — доступен YandexGPT</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="14" t="inlineStr">
+      <c r="A6" s="11" t="inlineStr">
         <is>
           <t>№2</t>
         </is>
       </c>
-      <c r="B6" s="14" t="inlineStr">
+      <c r="B6" s="11" t="inlineStr">
         <is>
           <t>О создании рабочей группы по мониторингу</t>
         </is>
       </c>
-      <c r="C6" s="14" t="inlineStr">
+      <c r="C6" s="11" t="inlineStr">
         <is>
           <t>Кандидат на канонический документ</t>
         </is>
       </c>
-      <c r="D6" s="14" t="inlineStr">
-        <is>
-          <t>Ни одна из шести legacy-записей пока не признана каноническим документом. Запись №2 является кандидатом на такой статус после проверки файла, метаданных, контрольной суммы и соответствия извлечённого текста. Одного хеша недостаточно: он подтверждает целостность файла, но не статус, актуальность и юридическую применимость.</t>
-        </is>
-      </c>
-      <c r="E6" s="14" t="inlineStr">
+      <c r="D6" s="11" t="inlineStr">
+        <is>
+          <t>Ни одна из шести legacy-записей пока не признана каноническим документом. Запись №2 — кандидат после проверки файла, метаданных, контрольной суммы и соответствия текста. Одного хеша недостаточно.</t>
+        </is>
+      </c>
+      <c r="E6" s="11" t="inlineStr">
         <is>
           <t>предполагаемо: загрузка файла (не подтверждено событием)</t>
         </is>
       </c>
-      <c r="F6" s="14" t="inlineStr">
+      <c r="F6" s="11" t="inlineStr">
         <is>
           <t>не проверено</t>
         </is>
       </c>
-      <c r="G6" s="14" t="inlineStr">
+      <c r="G6" s="11" t="inlineStr">
         <is>
           <t>подтверждён (файл), сверка хеша не выполнена</t>
         </is>
       </c>
+      <c r="H6" s="11" t="inlineStr">
+        <is>
+          <t>true — доступен YandexGPT</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="15" t="inlineStr">
+      <c r="A7" s="12" t="inlineStr">
         <is>
           <t>№3</t>
         </is>
       </c>
-      <c r="B7" s="15" t="inlineStr">
+      <c r="B7" s="12" t="inlineStr">
         <is>
           <t>Обоснование создания ЦЦиРТКД</t>
         </is>
       </c>
-      <c r="C7" s="15" t="inlineStr">
+      <c r="C7" s="12" t="inlineStr">
         <is>
           <t>Legacy OCR-представление, оригинал не связан</t>
         </is>
       </c>
-      <c r="D7" s="15" t="inlineStr">
-        <is>
-          <t>Текст получен из фото слайдов. Карточка источника-заглушки допустима, статус «канонический документ» не присваивается.</t>
-        </is>
-      </c>
-      <c r="E7" s="15" t="inlineStr">
+      <c r="D7" s="12" t="inlineStr">
+        <is>
+          <t>Текст получен из фото слайдов. Статус «канонический документ» не присваивается.</t>
+        </is>
+      </c>
+      <c r="E7" s="12" t="inlineStr">
         <is>
           <t>не установлено</t>
         </is>
       </c>
-      <c r="F7" s="15" t="inlineStr">
+      <c r="F7" s="12" t="inlineStr">
         <is>
           <t>не проверено</t>
         </is>
       </c>
-      <c r="G7" s="15" t="inlineStr">
+      <c r="G7" s="12" t="inlineStr">
         <is>
           <t>не связан</t>
         </is>
       </c>
+      <c r="H7" s="12" t="inlineStr">
+        <is>
+          <t>true — доступен YandexGPT</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="13" t="inlineStr">
+      <c r="A8" s="10" t="inlineStr">
         <is>
           <t>№4</t>
         </is>
       </c>
-      <c r="B8" s="13" t="inlineStr">
+      <c r="B8" s="10" t="inlineStr">
         <is>
           <t>Роль CDS Блока внутреннего контроля</t>
         </is>
       </c>
-      <c r="C8" s="13" t="inlineStr">
+      <c r="C8" s="10" t="inlineStr">
         <is>
           <t>Legacy-запись знания / сводка</t>
         </is>
       </c>
-      <c r="D8" s="13" t="inlineStr">
+      <c r="D8" s="10" t="inlineStr">
         <is>
           <t>Авторство и способ формирования не подтверждены журналом или событием создания.</t>
         </is>
       </c>
-      <c r="E8" s="13" t="inlineStr">
+      <c r="E8" s="10" t="inlineStr">
         <is>
           <t>не установлено</t>
         </is>
       </c>
-      <c r="F8" s="13" t="inlineStr">
+      <c r="F8" s="10" t="inlineStr">
         <is>
           <t>не проверено</t>
         </is>
       </c>
-      <c r="G8" s="13" t="inlineStr">
+      <c r="G8" s="10" t="inlineStr">
         <is>
           <t>не связан</t>
         </is>
       </c>
+      <c r="H8" s="10" t="inlineStr">
+        <is>
+          <t>true — доступен YandexGPT</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="15" t="inlineStr">
+      <c r="A9" s="12" t="inlineStr">
         <is>
           <t>№5</t>
         </is>
       </c>
-      <c r="B9" s="15" t="inlineStr">
+      <c r="B9" s="12" t="inlineStr">
         <is>
           <t>Концепция роли CDS</t>
         </is>
       </c>
-      <c r="C9" s="15" t="inlineStr">
+      <c r="C9" s="12" t="inlineStr">
         <is>
           <t>Legacy-представление, статус источника не подтверждён</t>
         </is>
       </c>
-      <c r="D9" s="15" t="inlineStr">
-        <is>
-          <t>original_title сохраняется без изменений. display_title = «Концепция роли CDS» (без слова «официальный»). Требует проверки источника целиком — полноты, редакции, статуса, не только юридической.</t>
-        </is>
-      </c>
-      <c r="E9" s="15" t="inlineStr">
+      <c r="D9" s="12" t="inlineStr">
+        <is>
+          <t>original_title сохраняется. display_title = «Концепция роли CDS» (без слова «официальный»).</t>
+        </is>
+      </c>
+      <c r="E9" s="12" t="inlineStr">
         <is>
           <t>не установлено</t>
         </is>
       </c>
-      <c r="F9" s="15" t="inlineStr">
+      <c r="F9" s="12" t="inlineStr">
         <is>
           <t>не проверено</t>
         </is>
       </c>
-      <c r="G9" s="15" t="inlineStr">
+      <c r="G9" s="12" t="inlineStr">
         <is>
           <t>не связан</t>
         </is>
       </c>
+      <c r="H9" s="12" t="inlineStr">
+        <is>
+          <t>true — доступен YandexGPT</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="15" t="inlineStr">
+      <c r="A10" s="12" t="inlineStr">
         <is>
           <t>№6</t>
         </is>
       </c>
-      <c r="B10" s="15" t="inlineStr">
+      <c r="B10" s="12" t="inlineStr">
         <is>
           <t>Положение о ДВКиК (перенос из чата)</t>
         </is>
       </c>
-      <c r="C10" s="15" t="inlineStr">
+      <c r="C10" s="12" t="inlineStr">
         <is>
           <t>Legacy OCR-представление, оригинал не связан</t>
         </is>
       </c>
-      <c r="D10" s="15" t="inlineStr">
-        <is>
-          <t>Постраничная структура не подтверждена. Локатор — legacy_chunk_index, НЕ виртуальная страница 1.</t>
-        </is>
-      </c>
-      <c r="E10" s="15" t="inlineStr">
+      <c r="D10" s="12" t="inlineStr">
+        <is>
+          <t>Постраничная структура не подтверждена. Локатор — legacy_chunk_index, НЕ виртуальная страница 1. РЕАЛЬНЫЙ внутренний документ Банка — см. Risk Register RR-001.</t>
+        </is>
+      </c>
+      <c r="E10" s="12" t="inlineStr">
         <is>
           <t>распознано OCR + ручной перенос (не подтверждено журналом)</t>
         </is>
       </c>
-      <c r="F10" s="15" t="inlineStr">
+      <c r="F10" s="12" t="inlineStr">
         <is>
           <t>не проверено</t>
         </is>
       </c>
-      <c r="G10" s="15" t="inlineStr">
+      <c r="G10" s="12" t="inlineStr">
         <is>
           <t>не связан</t>
+        </is>
+      </c>
+      <c r="H10" s="12" t="inlineStr">
+        <is>
+          <t>true — доступен YandexGPT</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A2:I2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2503,372 +3253,372 @@
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="42" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="60" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="55" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="10" t="inlineStr">
-        <is>
-          <t>Таблица соответствия полей exec_knowledge → целевая модель (исправленная)</t>
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>Таблица соответствия полей exec_knowledge → целевая модель</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="11" t="inlineStr">
-        <is>
-          <t>summary не в title; use_in_ai/priority — политика использования, а не свойство документа</t>
+      <c r="A2" s="8" t="inlineStr">
+        <is>
+          <t>use_in_ai помечен как требующий немедленного пересмотра — см. Risk Register RR-001</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="12" t="inlineStr">
+      <c r="A4" s="9" t="inlineStr">
         <is>
           <t>Поле exec_knowledge</t>
         </is>
       </c>
-      <c r="B4" s="12" t="inlineStr">
+      <c r="B4" s="9" t="inlineStr">
         <is>
           <t>Целевой объект.поле</t>
         </is>
       </c>
-      <c r="C4" s="12" t="inlineStr">
+      <c r="C4" s="9" t="inlineStr">
         <is>
           <t>Переносится автоматически</t>
         </is>
       </c>
-      <c r="D4" s="12" t="inlineStr">
+      <c r="D4" s="9" t="inlineStr">
         <is>
           <t>Требует проверки</t>
         </is>
       </c>
-      <c r="E4" s="12" t="inlineStr">
+      <c r="E4" s="9" t="inlineStr">
         <is>
           <t>Комментарий</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="16" t="inlineStr">
+      <c r="A5" s="13" t="inlineStr">
         <is>
           <t>title</t>
         </is>
       </c>
-      <c r="B5" s="16" t="inlineStr">
+      <c r="B5" s="13" t="inlineStr">
         <is>
           <t>source_document.original_title / display_title</t>
         </is>
       </c>
-      <c r="C5" s="16" t="inlineStr">
+      <c r="C5" s="13" t="inlineStr">
         <is>
           <t>да, в original_title</t>
         </is>
       </c>
-      <c r="D5" s="16" t="inlineStr">
+      <c r="D5" s="13" t="inlineStr">
         <is>
           <t>нет</t>
         </is>
       </c>
-      <c r="E5" s="16" t="inlineStr">
-        <is>
-          <t>title копируется как original_title без изменений; display_title формируется отдельно и может отличаться</t>
+      <c r="E5" s="13" t="inlineStr">
+        <is>
+          <t>title копируется как original_title без изменений; display_title формируется отдельно</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="16" t="inlineStr">
+      <c r="A6" s="13" t="inlineStr">
         <is>
           <t>summary</t>
         </is>
       </c>
-      <c r="B6" s="16" t="inlineStr">
+      <c r="B6" s="13" t="inlineStr">
         <is>
           <t>document_annotation.summary (отдельное поле аннотации)</t>
         </is>
       </c>
-      <c r="C6" s="16" t="inlineStr">
+      <c r="C6" s="13" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="D6" s="16" t="inlineStr">
+      <c r="D6" s="13" t="inlineStr">
         <is>
           <t>нет</t>
         </is>
       </c>
-      <c r="E6" s="16" t="inlineStr">
-        <is>
-          <t>НЕ переносится в title — это самостоятельное поле аннотации, не заголовок</t>
+      <c r="E6" s="13" t="inlineStr">
+        <is>
+          <t>НЕ переносится в title</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="16" t="inlineStr">
+      <c r="A7" s="13" t="inlineStr">
         <is>
           <t>doc_type</t>
         </is>
       </c>
-      <c r="B7" s="16" t="inlineStr">
+      <c r="B7" s="13" t="inlineStr">
         <is>
           <t>требует нормализации, не source_type напрямую</t>
         </is>
       </c>
-      <c r="C7" s="16" t="inlineStr">
+      <c r="C7" s="13" t="inlineStr">
         <is>
           <t>нет</t>
         </is>
       </c>
-      <c r="D7" s="16" t="inlineStr">
+      <c r="D7" s="13" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="E7" s="16" t="inlineStr">
-        <is>
-          <t>matrix/note/other/policy — категории использования в кабинете, не тип первоисточника. Нужен маппинг вручную</t>
+      <c r="E7" s="13" t="inlineStr">
+        <is>
+          <t>категории использования в кабинете, не тип первоисточника</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="16" t="inlineStr">
+      <c r="A8" s="13" t="inlineStr">
         <is>
           <t>body</t>
         </is>
       </c>
-      <c r="B8" s="16" t="inlineStr">
+      <c r="B8" s="13" t="inlineStr">
         <is>
           <t>document_chunk.content (через legacy locator)</t>
         </is>
       </c>
-      <c r="C8" s="16" t="inlineStr">
+      <c r="C8" s="13" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="D8" s="16" t="inlineStr">
+      <c r="D8" s="13" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="E8" s="16" t="inlineStr">
-        <is>
-          <t>переносится как есть, но БЕЗ создания фиктивной 'страницы 1'</t>
+      <c r="E8" s="13" t="inlineStr">
+        <is>
+          <t>БЕЗ создания фиктивной 'страницы 1'</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="16" t="inlineStr">
+      <c r="A9" s="13" t="inlineStr">
         <is>
           <t>filename</t>
         </is>
       </c>
-      <c r="B9" s="16" t="inlineStr">
+      <c r="B9" s="13" t="inlineStr">
         <is>
           <t>source_document.original_filename</t>
         </is>
       </c>
-      <c r="C9" s="16" t="inlineStr">
+      <c r="C9" s="13" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="D9" s="16" t="inlineStr">
+      <c r="D9" s="13" t="inlineStr">
         <is>
           <t>нет</t>
         </is>
       </c>
-      <c r="E9" s="16" t="inlineStr">
+      <c r="E9" s="13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="16" t="inlineStr">
+      <c r="A10" s="13" t="inlineStr">
         <is>
           <t>file_type</t>
         </is>
       </c>
-      <c r="B10" s="16" t="inlineStr">
+      <c r="B10" s="13" t="inlineStr">
         <is>
           <t>source_document.file_type</t>
         </is>
       </c>
-      <c r="C10" s="16" t="inlineStr">
+      <c r="C10" s="13" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="D10" s="16" t="inlineStr">
+      <c r="D10" s="13" t="inlineStr">
         <is>
           <t>нет</t>
         </is>
       </c>
-      <c r="E10" s="16" t="inlineStr">
+      <c r="E10" s="13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="16" t="inlineStr">
+      <c r="A11" s="13" t="inlineStr">
         <is>
           <t>s3_key</t>
         </is>
       </c>
-      <c r="B11" s="16" t="inlineStr">
+      <c r="B11" s="13" t="inlineStr">
         <is>
           <t>source_document.s3_key (только если IS NOT NULL)</t>
         </is>
       </c>
-      <c r="C11" s="16" t="inlineStr">
+      <c r="C11" s="13" t="inlineStr">
         <is>
           <t>да, для №2 только</t>
         </is>
       </c>
-      <c r="D11" s="16" t="inlineStr">
+      <c r="D11" s="13" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="E11" s="16" t="inlineStr">
-        <is>
-          <t>у 5 из 6 записей — NULL, переносить нечего; для №2 — сверить хеш перед пометкой 'подтверждён'</t>
+      <c r="E11" s="13" t="inlineStr">
+        <is>
+          <t>у 5 из 6 — NULL</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="16" t="inlineStr">
+      <c r="A12" s="13" t="inlineStr">
         <is>
           <t>page_count</t>
         </is>
       </c>
-      <c r="B12" s="16" t="inlineStr">
+      <c r="B12" s="13" t="inlineStr">
         <is>
           <t>source_document.page_count</t>
         </is>
       </c>
-      <c r="C12" s="16" t="inlineStr">
+      <c r="C12" s="13" t="inlineStr">
         <is>
           <t>нет</t>
         </is>
       </c>
-      <c r="D12" s="16" t="inlineStr">
+      <c r="D12" s="13" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="E12" s="16" t="inlineStr">
-        <is>
-          <t>NULL остаётся 'не установлено', НЕ вычисляется предположительно</t>
+      <c r="E12" s="13" t="inlineStr">
+        <is>
+          <t>NULL остаётся 'не установлено'</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="16" t="inlineStr">
+      <c r="A13" s="13" t="inlineStr">
         <is>
           <t>use_in_ai</t>
         </is>
       </c>
-      <c r="B13" s="16" t="inlineStr">
+      <c r="B13" s="13" t="inlineStr">
         <is>
           <t>knowledge_usage_policy.ai_context_enabled</t>
         </is>
       </c>
-      <c r="C13" s="16" t="inlineStr">
+      <c r="C13" s="13" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="D13" s="16" t="inlineStr">
+      <c r="D13" s="13" t="inlineStr">
+        <is>
+          <t>да (см. RR-001)</t>
+        </is>
+      </c>
+      <c r="E13" s="13" t="inlineStr">
+        <is>
+          <t>политика использования знания в AI-контексте; ТРЕБУЕТ немедленного пересмотра значений</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="13" t="inlineStr">
+        <is>
+          <t>priority</t>
+        </is>
+      </c>
+      <c r="B14" s="13" t="inlineStr">
+        <is>
+          <t>knowledge_usage_policy.priority</t>
+        </is>
+      </c>
+      <c r="C14" s="13" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="D14" s="13" t="inlineStr">
         <is>
           <t>нет</t>
         </is>
       </c>
-      <c r="E13" s="16" t="inlineStr">
-        <is>
-          <t>это политика использования КОНКРЕТНОЙ версии/знания в AI-контексте, не свойство документа в целом</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="16" t="inlineStr">
-        <is>
-          <t>priority</t>
-        </is>
-      </c>
-      <c r="B14" s="16" t="inlineStr">
-        <is>
-          <t>knowledge_usage_policy.priority</t>
-        </is>
-      </c>
-      <c r="C14" s="16" t="inlineStr">
+      <c r="E14" s="13" t="inlineStr">
+        <is>
+          <t>ранжирование в AI-контексте</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="13" t="inlineStr">
+        <is>
+          <t>created_by</t>
+        </is>
+      </c>
+      <c r="B15" s="13" t="inlineStr">
+        <is>
+          <t>НЕ переносится в who_uploaded автоматически</t>
+        </is>
+      </c>
+      <c r="C15" s="13" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="D15" s="13" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="D14" s="16" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="E14" s="16" t="inlineStr">
-        <is>
-          <t>относится к ранжированию в AI-контексте, не к документу как таковому</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="16" t="inlineStr">
-        <is>
-          <t>created_by</t>
-        </is>
-      </c>
-      <c r="B15" s="16" t="inlineStr">
-        <is>
-          <t>НЕ переносится в who_uploaded автоматически</t>
-        </is>
-      </c>
-      <c r="C15" s="16" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="D15" s="16" t="inlineStr">
+      <c r="E15" s="13" t="inlineStr">
+        <is>
+          <t>если NULL → 'не установлено'</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="13" t="inlineStr">
+        <is>
+          <t>exec_knowledge_chunk.page_number</t>
+        </is>
+      </c>
+      <c r="B16" s="13" t="inlineStr">
+        <is>
+          <t>document_chunk.locator_type + legacy_chunk_index</t>
+        </is>
+      </c>
+      <c r="C16" s="13" t="inlineStr">
+        <is>
+          <t>да, как locator</t>
+        </is>
+      </c>
+      <c r="D16" s="13" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="E15" s="16" t="inlineStr">
-        <is>
-          <t>если created_by=NULL, who_uploaded='не установлено'; если created_by=email — переносится как 'предполагаемый автор', требует пометки</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="16" t="inlineStr">
-        <is>
-          <t>exec_knowledge_chunk.page_number</t>
-        </is>
-      </c>
-      <c r="B16" s="16" t="inlineStr">
-        <is>
-          <t>document_chunk.locator_type + legacy_chunk_index</t>
-        </is>
-      </c>
-      <c r="C16" s="16" t="inlineStr">
-        <is>
-          <t>да, как locator</t>
-        </is>
-      </c>
-      <c r="D16" s="16" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="E16" s="16" t="inlineStr">
-        <is>
-          <t>NULL page_number НЕ становится 1 — остаётся 'страница не установлена'</t>
+      <c r="E16" s="13" t="inlineStr">
+        <is>
+          <t>NULL остаётся 'страница не установлена'</t>
         </is>
       </c>
     </row>
@@ -2898,230 +3648,230 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="10" t="inlineStr">
+      <c r="A1" s="7" t="inlineStr">
         <is>
           <t>Маршрут перехода: legacy → shadow → canonical</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="11" t="inlineStr">
+      <c r="A2" s="8" t="inlineStr">
         <is>
           <t>Переключение продуктивного контура запрещено до отдельного решения после shadow-периода</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="12" t="inlineStr">
+      <c r="A4" s="9" t="inlineStr">
         <is>
           <t>Шаг</t>
         </is>
       </c>
-      <c r="B4" s="12" t="inlineStr">
+      <c r="B4" s="9" t="inlineStr">
         <is>
           <t>Режим</t>
         </is>
       </c>
-      <c r="C4" s="12" t="inlineStr">
+      <c r="C4" s="9" t="inlineStr">
         <is>
           <t>Действие</t>
         </is>
       </c>
-      <c r="D4" s="12" t="inlineStr">
+      <c r="D4" s="9" t="inlineStr">
         <is>
           <t>Тип операции</t>
         </is>
       </c>
-      <c r="E4" s="12" t="inlineStr">
+      <c r="E4" s="9" t="inlineStr">
         <is>
           <t>Статус</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="16" t="inlineStr">
+      <c r="A5" s="13" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B5" s="16" t="inlineStr">
+      <c r="B5" s="13" t="inlineStr">
         <is>
           <t>legacy</t>
         </is>
       </c>
-      <c r="C5" s="16" t="inlineStr">
-        <is>
-          <t>Текущее состояние: exec-planner-ai читает exec_knowledge напрямую</t>
-        </is>
-      </c>
-      <c r="D5" s="16" t="inlineStr">
+      <c r="C5" s="13" t="inlineStr">
+        <is>
+          <t>Текущее состояние: exec-planner-ai читает exec_knowledge напрямую, все 6 записей с use_in_ai=true</t>
+        </is>
+      </c>
+      <c r="D5" s="13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E5" s="16" t="inlineStr">
+      <c r="E5" s="13" t="inlineStr">
         <is>
           <t>действует сейчас</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="16" t="inlineStr">
+      <c r="A6" s="13" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B6" s="16" t="inlineStr">
+      <c r="B6" s="13" t="inlineStr">
         <is>
           <t>legacy</t>
         </is>
       </c>
-      <c r="C6" s="16" t="inlineStr">
-        <is>
-          <t>Создать source_document-заглушки для №2,3,4,5,6 со статусом source_status='не установлен', processing_status='загружен'</t>
-        </is>
-      </c>
-      <c r="D6" s="16" t="inlineStr">
+      <c r="C6" s="13" t="inlineStr">
+        <is>
+          <t>Создать source_document-заглушки для №2,3,4,5,6</t>
+        </is>
+      </c>
+      <c r="D6" s="13" t="inlineStr">
         <is>
           <t>миграция схемы БД (после утверждения)</t>
         </is>
       </c>
-      <c r="E6" s="16" t="inlineStr">
+      <c r="E6" s="13" t="inlineStr">
         <is>
           <t>не выполнено</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="16" t="inlineStr">
+      <c r="A7" s="13" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B7" s="16" t="inlineStr">
+      <c r="B7" s="13" t="inlineStr">
         <is>
           <t>legacy</t>
         </is>
       </c>
-      <c r="C7" s="16" t="inlineStr">
-        <is>
-          <t>№1 переносится параллельно как structured_work_artifact, без немедленного превращения в structured-сущности</t>
-        </is>
-      </c>
-      <c r="D7" s="16" t="inlineStr">
-        <is>
-          <t>требует отдельного проектирования структуры стейкхолдеров</t>
-        </is>
-      </c>
-      <c r="E7" s="16" t="inlineStr">
+      <c r="C7" s="13" t="inlineStr">
+        <is>
+          <t>№1 переносится как structured_work_artifact</t>
+        </is>
+      </c>
+      <c r="D7" s="13" t="inlineStr">
+        <is>
+          <t>требует отдельного проектирования</t>
+        </is>
+      </c>
+      <c r="E7" s="13" t="inlineStr">
         <is>
           <t>не выполнено</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="16" t="inlineStr">
+      <c r="A8" s="13" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B8" s="16" t="inlineStr">
+      <c r="B8" s="13" t="inlineStr">
         <is>
           <t>shadow</t>
         </is>
       </c>
-      <c r="C8" s="16" t="inlineStr">
-        <is>
-          <t>exec-planner-ai получает feature flag knowledge_source_mode. В shadow формируются ДВЕ выборки: legacy (используется) + canonical (логируется, не используется)</t>
-        </is>
-      </c>
-      <c r="D8" s="16" t="inlineStr">
+      <c r="C8" s="13" t="inlineStr">
+        <is>
+          <t>feature flag knowledge_source_mode; в shadow — две выборки, вторая не влияет на ответ</t>
+        </is>
+      </c>
+      <c r="D8" s="13" t="inlineStr">
         <is>
           <t>разработка backend</t>
         </is>
       </c>
-      <c r="E8" s="16" t="inlineStr">
+      <c r="E8" s="13" t="inlineStr">
         <is>
           <t>не выполнено</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="16" t="inlineStr">
+      <c r="A9" s="13" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B9" s="16" t="inlineStr">
+      <c r="B9" s="13" t="inlineStr">
         <is>
           <t>shadow</t>
         </is>
       </c>
-      <c r="C9" s="16" t="inlineStr">
-        <is>
-          <t>Сравнение: состав и порядок фрагментов, объём токенов, релевантность, время ответа, качество цитат — за период не менее 2 недель реального использования</t>
-        </is>
-      </c>
-      <c r="D9" s="16" t="inlineStr">
+      <c r="C9" s="13" t="inlineStr">
+        <is>
+          <t>Сравнение состава фрагментов, релевантности, качества цитат — не менее 2 недель</t>
+        </is>
+      </c>
+      <c r="D9" s="13" t="inlineStr">
         <is>
           <t>аналитика по логам</t>
         </is>
       </c>
-      <c r="E9" s="16" t="inlineStr">
+      <c r="E9" s="13" t="inlineStr">
         <is>
           <t>не выполнено</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="16" t="inlineStr">
+      <c r="A10" s="13" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="B10" s="16" t="inlineStr">
+      <c r="B10" s="13" t="inlineStr">
         <is>
           <t>canonical</t>
         </is>
       </c>
-      <c r="C10" s="16" t="inlineStr">
-        <is>
-          <t>Переключение knowledge_source_mode=canonical только после ручной приёмки результатов shadow-периода</t>
-        </is>
-      </c>
-      <c r="D10" s="16" t="inlineStr">
+      <c r="C10" s="13" t="inlineStr">
+        <is>
+          <t>Переключение только после ручной приёмки результатов shadow-периода</t>
+        </is>
+      </c>
+      <c r="D10" s="13" t="inlineStr">
         <is>
           <t>решение руководителя</t>
         </is>
       </c>
-      <c r="E10" s="16" t="inlineStr">
+      <c r="E10" s="13" t="inlineStr">
         <is>
           <t>не выполнено</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="16" t="inlineStr">
+      <c r="A11" s="13" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="B11" s="16" t="inlineStr">
+      <c r="B11" s="13" t="inlineStr">
         <is>
           <t>canonical</t>
         </is>
       </c>
-      <c r="C11" s="16" t="inlineStr">
-        <is>
-          <t>exec_knowledge помечается is_legacy=true, скрывается из формы загрузки новых записей, но НЕ удаляется</t>
-        </is>
-      </c>
-      <c r="D11" s="16" t="inlineStr">
+      <c r="C11" s="13" t="inlineStr">
+        <is>
+          <t>exec_knowledge помечается is_legacy=true, НЕ удаляется</t>
+        </is>
+      </c>
+      <c r="D11" s="13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E11" s="16" t="inlineStr">
+      <c r="E11" s="13" t="inlineStr">
         <is>
           <t>не выполнено</t>
         </is>
@@ -3146,110 +3896,110 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
     <col width="55" customWidth="1" min="3" max="3"/>
-    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="10" t="inlineStr">
+      <c r="A1" s="7" t="inlineStr">
         <is>
           <t>План отката по этапам миграции</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="11" t="inlineStr">
+      <c r="A2" s="8" t="inlineStr">
         <is>
           <t>Формальный план вместо формулировки «откат одной строкой SQL»</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="12" t="inlineStr">
+      <c r="A4" s="9" t="inlineStr">
         <is>
           <t>Сценарий отката</t>
         </is>
       </c>
-      <c r="B4" s="12" t="inlineStr">
+      <c r="B4" s="9" t="inlineStr">
         <is>
           <t>Уровень риска</t>
         </is>
       </c>
-      <c r="C4" s="12" t="inlineStr">
+      <c r="C4" s="9" t="inlineStr">
         <is>
           <t>Действие</t>
         </is>
       </c>
-      <c r="D4" s="12" t="inlineStr">
+      <c r="D4" s="9" t="inlineStr">
         <is>
           <t>Потеря данных</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="16" t="inlineStr">
+      <c r="A5" s="13" t="inlineStr">
         <is>
           <t>Откат из shadow</t>
         </is>
       </c>
-      <c r="B5" s="16" t="inlineStr">
+      <c r="B5" s="13" t="inlineStr">
         <is>
           <t>Низкий — контур не влияет на ответ пользователю</t>
         </is>
       </c>
-      <c r="C5" s="16" t="inlineStr">
+      <c r="C5" s="13" t="inlineStr">
         <is>
           <t>Отключить сбор теневой выборки (feature flag → legacy)</t>
         </is>
       </c>
-      <c r="D5" s="16" t="inlineStr">
-        <is>
-          <t>нет, теневые логи не используются в ответах</t>
+      <c r="D5" s="13" t="inlineStr">
+        <is>
+          <t>нет</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="16" t="inlineStr">
+      <c r="A6" s="13" t="inlineStr">
         <is>
           <t>Откат из canonical (сразу после переключения)</t>
         </is>
       </c>
-      <c r="B6" s="16" t="inlineStr">
-        <is>
-          <t>Средний — ответы ИИ уже формируются по новому контуру</t>
-        </is>
-      </c>
-      <c r="C6" s="16" t="inlineStr">
-        <is>
-          <t>feature flag knowledge_source_mode → legacy. exec_knowledge не удалена, выборка восстанавливается немедленно</t>
-        </is>
-      </c>
-      <c r="D6" s="16" t="inlineStr">
-        <is>
-          <t>нет потери — старые данные не удалялись</t>
+      <c r="B6" s="13" t="inlineStr">
+        <is>
+          <t>Средний</t>
+        </is>
+      </c>
+      <c r="C6" s="13" t="inlineStr">
+        <is>
+          <t>feature flag → legacy, exec_knowledge не удалена</t>
+        </is>
+      </c>
+      <c r="D6" s="13" t="inlineStr">
+        <is>
+          <t>нет</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="16" t="inlineStr">
+      <c r="A7" s="13" t="inlineStr">
         <is>
           <t>Откат после структурирования матрицы стейкхолдеров (№1)</t>
         </is>
       </c>
-      <c r="B7" s="16" t="inlineStr">
-        <is>
-          <t>Выше — структурные сущности могли получить собственные правки</t>
-        </is>
-      </c>
-      <c r="C7" s="16" t="inlineStr">
-        <is>
-          <t>structured-сущности помечаются архивными, legacy-запись остаётся источником истины до повторного решения</t>
-        </is>
-      </c>
-      <c r="D7" s="16" t="inlineStr">
-        <is>
-          <t>риск расхождения правок, требует сверки перед повторным откатом</t>
+      <c r="B7" s="13" t="inlineStr">
+        <is>
+          <t>Выше</t>
+        </is>
+      </c>
+      <c r="C7" s="13" t="inlineStr">
+        <is>
+          <t>structured-сущности помечаются архивными, legacy-запись остаётся источником истины</t>
+        </is>
+      </c>
+      <c r="D7" s="13" t="inlineStr">
+        <is>
+          <t>риск расхождения правок</t>
         </is>
       </c>
     </row>
@@ -3280,460 +4030,460 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="10" t="inlineStr">
-        <is>
-          <t>Расширенная матрица ролей и полномочий (RBAC)</t>
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>Расширенная матрица ролей и полномочий (RBAC) — ПРОЕКТНОЕ ТРЕБОВАНИЕ</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="11" t="inlineStr">
-        <is>
-          <t>Область полномочий: Блок / подразделение / проект / документ. Критические действия требуют усиленного подтверждения</t>
+      <c r="A2" s="8" t="inlineStr">
+        <is>
+          <t>ВАЖНО: это целевая модель. Технически сейчас в системе НЕТ разграничения по документам — есть только общая роль кабинета (exec_cabinet_access). Роль 'ИИ-агент' в строке ниже описывает ЖЕЛАЕМОЕ поведение, а не текущий технический контроль — фактические права backend см. лист 11</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="12" t="inlineStr">
+      <c r="A4" s="9" t="inlineStr">
         <is>
           <t>Роль</t>
         </is>
       </c>
-      <c r="B4" s="12" t="inlineStr">
+      <c r="B4" s="9" t="inlineStr">
         <is>
           <t>Полномочия</t>
         </is>
       </c>
-      <c r="C4" s="12" t="inlineStr">
+      <c r="C4" s="9" t="inlineStr">
         <is>
           <t>Область действия</t>
         </is>
       </c>
-      <c r="D4" s="12" t="inlineStr">
+      <c r="D4" s="9" t="inlineStr">
         <is>
           <t>Временное делегирование</t>
         </is>
       </c>
-      <c r="E4" s="12" t="inlineStr">
+      <c r="E4" s="9" t="inlineStr">
         <is>
           <t>Замещение на период отсутствия</t>
         </is>
       </c>
-      <c r="F4" s="12" t="inlineStr">
+      <c r="F4" s="9" t="inlineStr">
         <is>
           <t>Запрет самосогласования</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="16" t="inlineStr">
+      <c r="A5" s="13" t="inlineStr">
         <is>
           <t>Автор</t>
         </is>
       </c>
-      <c r="B5" s="16" t="inlineStr">
+      <c r="B5" s="13" t="inlineStr">
         <is>
           <t>создаёт черновик записи/документа</t>
         </is>
       </c>
-      <c r="C5" s="16" t="inlineStr">
+      <c r="C5" s="13" t="inlineStr">
         <is>
           <t>свой черновик</t>
         </is>
       </c>
-      <c r="D5" s="16" t="inlineStr">
+      <c r="D5" s="13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E5" s="16" t="inlineStr">
+      <c r="E5" s="13" t="inlineStr">
         <is>
           <t>нет</t>
         </is>
       </c>
-      <c r="F5" s="16" t="inlineStr">
+      <c r="F5" s="13" t="inlineStr">
         <is>
           <t>нет</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="16" t="inlineStr">
+      <c r="A6" s="13" t="inlineStr">
         <is>
           <t>Владелец документа</t>
         </is>
       </c>
-      <c r="B6" s="16" t="inlineStr">
-        <is>
-          <t>утверждает статус источника, редакции, применимость своего документа</t>
-        </is>
-      </c>
-      <c r="C6" s="16" t="inlineStr">
+      <c r="B6" s="13" t="inlineStr">
+        <is>
+          <t>утверждает статус источника, редакции, применимость</t>
+        </is>
+      </c>
+      <c r="C6" s="13" t="inlineStr">
         <is>
           <t>документ, за который назначен</t>
         </is>
       </c>
-      <c r="D6" s="16" t="inlineStr">
+      <c r="D6" s="13" t="inlineStr">
         <is>
           <t>может назначаться временно</t>
         </is>
       </c>
-      <c r="E6" s="16" t="inlineStr">
+      <c r="E6" s="13" t="inlineStr">
         <is>
           <t>да, на срок делегирования</t>
         </is>
       </c>
-      <c r="F6" s="16" t="inlineStr">
-        <is>
-          <t>нет — не может утвердить документ, который сам загрузил как черновик, если требуется разделение обязанностей</t>
+      <c r="F6" s="13" t="inlineStr">
+        <is>
+          <t>нет — не может утвердить документ, который сам загрузил как черновик</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="16" t="inlineStr">
+      <c r="A7" s="13" t="inlineStr">
         <is>
           <t>Владелец процесса</t>
         </is>
       </c>
-      <c r="B7" s="16" t="inlineStr">
-        <is>
-          <t>подтверждает применимость документа к процессу, владеет эффектом процесса</t>
-        </is>
-      </c>
-      <c r="C7" s="16" t="inlineStr">
+      <c r="B7" s="13" t="inlineStr">
+        <is>
+          <t>подтверждает применимость документа к процессу</t>
+        </is>
+      </c>
+      <c r="C7" s="13" t="inlineStr">
         <is>
           <t>процесс/функция</t>
         </is>
       </c>
-      <c r="D7" s="16" t="inlineStr">
+      <c r="D7" s="13" t="inlineStr">
         <is>
           <t>может назначаться временно</t>
         </is>
       </c>
-      <c r="E7" s="16" t="inlineStr">
+      <c r="E7" s="13" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="F7" s="16" t="inlineStr">
+      <c r="F7" s="13" t="inlineStr">
         <is>
           <t>нет</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="16" t="inlineStr">
+      <c r="A8" s="13" t="inlineStr">
         <is>
           <t>Проверяющий (верификатор)</t>
         </is>
       </c>
-      <c r="B8" s="16" t="inlineStr">
-        <is>
-          <t>выставляет все значения статуса верификации</t>
-        </is>
-      </c>
-      <c r="C8" s="16" t="inlineStr">
+      <c r="B8" s="13" t="inlineStr">
+        <is>
+          <t>выставляет значения статуса верификации</t>
+        </is>
+      </c>
+      <c r="C8" s="13" t="inlineStr">
         <is>
           <t>документ/справочник/сопоставление</t>
         </is>
       </c>
-      <c r="D8" s="16" t="inlineStr">
+      <c r="D8" s="13" t="inlineStr">
         <is>
           <t>может назначаться на документ</t>
         </is>
       </c>
-      <c r="E8" s="16" t="inlineStr">
-        <is>
-          <t>да, есть право замещения</t>
-        </is>
-      </c>
-      <c r="F8" s="16" t="inlineStr">
+      <c r="E8" s="13" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="F8" s="13" t="inlineStr">
         <is>
           <t>да — не может проверять документ, который сам создал</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="16" t="inlineStr">
+      <c r="A9" s="13" t="inlineStr">
         <is>
           <t>Согласующий</t>
         </is>
       </c>
-      <c r="B9" s="16" t="inlineStr">
-        <is>
-          <t>переводит между 'на рассмотрении', 'замечания', 'отклонено'</t>
-        </is>
-      </c>
-      <c r="C9" s="16" t="inlineStr">
+      <c r="B9" s="13" t="inlineStr">
+        <is>
+          <t>переводит между 'на рассмотрении'/'замечания'/'отклонено'</t>
+        </is>
+      </c>
+      <c r="C9" s="13" t="inlineStr">
         <is>
           <t>инициатива/проект/функция</t>
         </is>
       </c>
-      <c r="D9" s="16" t="inlineStr">
-        <is>
-          <t>может делегироваться на период отсутствия</t>
-        </is>
-      </c>
-      <c r="E9" s="16" t="inlineStr">
+      <c r="D9" s="13" t="inlineStr">
+        <is>
+          <t>может делегироваться</t>
+        </is>
+      </c>
+      <c r="E9" s="13" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="F9" s="16" t="inlineStr">
+      <c r="F9" s="13" t="inlineStr">
         <is>
           <t>да — не может согласовать собственное предложение</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="16" t="inlineStr">
+      <c r="A10" s="13" t="inlineStr">
         <is>
           <t>Утверждающий</t>
         </is>
       </c>
-      <c r="B10" s="16" t="inlineStr">
+      <c r="B10" s="13" t="inlineStr">
         <is>
           <t>единственный, кто переводит в 'согласовано'/'утверждено'</t>
         </is>
       </c>
-      <c r="C10" s="16" t="inlineStr">
-        <is>
-          <t>Блок/подразделение/проект — по области полномочий</t>
-        </is>
-      </c>
-      <c r="D10" s="16" t="inlineStr">
+      <c r="C10" s="13" t="inlineStr">
+        <is>
+          <t>Блок/подразделение/проект</t>
+        </is>
+      </c>
+      <c r="D10" s="13" t="inlineStr">
         <is>
           <t>делегирование только с усиленным подтверждением</t>
         </is>
       </c>
-      <c r="E10" s="16" t="inlineStr">
+      <c r="E10" s="13" t="inlineStr">
         <is>
           <t>да, фиксируется отдельно</t>
         </is>
       </c>
-      <c r="F10" s="16" t="inlineStr">
+      <c r="F10" s="13" t="inlineStr">
         <is>
           <t>да, всегда</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="16" t="inlineStr">
+      <c r="A11" s="13" t="inlineStr">
         <is>
           <t>Контролёр поручения</t>
         </is>
       </c>
-      <c r="B11" s="16" t="inlineStr">
-        <is>
-          <t>принимает отчёт по поручению, снимает с контроля</t>
-        </is>
-      </c>
-      <c r="C11" s="16" t="inlineStr">
+      <c r="B11" s="13" t="inlineStr">
+        <is>
+          <t>принимает отчёт, снимает с контроля</t>
+        </is>
+      </c>
+      <c r="C11" s="13" t="inlineStr">
         <is>
           <t>конкретное поручение</t>
         </is>
       </c>
-      <c r="D11" s="16" t="inlineStr">
-        <is>
-          <t>может замещаться на период отсутствия</t>
-        </is>
-      </c>
-      <c r="E11" s="16" t="inlineStr">
+      <c r="D11" s="13" t="inlineStr">
+        <is>
+          <t>может замещаться</t>
+        </is>
+      </c>
+      <c r="E11" s="13" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="F11" s="16" t="inlineStr">
-        <is>
-          <t>да — не может быть исполнителем того же поручения</t>
+      <c r="F11" s="13" t="inlineStr">
+        <is>
+          <t>да</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="16" t="inlineStr">
+      <c r="A12" s="13" t="inlineStr">
         <is>
           <t>Администратор данных</t>
         </is>
       </c>
-      <c r="B12" s="16" t="inlineStr">
+      <c r="B12" s="13" t="inlineStr">
         <is>
           <t>правит справочники, оргструктуру, архивирует</t>
         </is>
       </c>
-      <c r="C12" s="16" t="inlineStr">
+      <c r="C12" s="13" t="inlineStr">
         <is>
           <t>весь контур справочников</t>
         </is>
       </c>
-      <c r="D12" s="16" t="inlineStr">
+      <c r="D12" s="13" t="inlineStr">
         <is>
           <t>нет</t>
         </is>
       </c>
-      <c r="E12" s="16" t="inlineStr">
-        <is>
-          <t>да, для отпуска/болезни</t>
-        </is>
-      </c>
-      <c r="F12" s="16" t="inlineStr">
+      <c r="E12" s="13" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="F12" s="13" t="inlineStr">
         <is>
           <t>нет</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="16" t="inlineStr">
+      <c r="A13" s="13" t="inlineStr">
         <is>
           <t>Системный администратор</t>
         </is>
       </c>
-      <c r="B13" s="16" t="inlineStr">
+      <c r="B13" s="13" t="inlineStr">
         <is>
           <t>управляет доступом, ролями, feature flags</t>
         </is>
       </c>
-      <c r="C13" s="16" t="inlineStr">
+      <c r="C13" s="13" t="inlineStr">
         <is>
           <t>вся платформа</t>
         </is>
       </c>
-      <c r="D13" s="16" t="inlineStr">
+      <c r="D13" s="13" t="inlineStr">
         <is>
           <t>нет</t>
         </is>
       </c>
-      <c r="E13" s="16" t="inlineStr">
+      <c r="E13" s="13" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="F13" s="16" t="inlineStr">
-        <is>
-          <t>нет — критические действия требуют усиленного подтверждения</t>
+      <c r="F13" s="13" t="inlineStr">
+        <is>
+          <t>нет — требует усиленного подтверждения</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="16" t="inlineStr">
+      <c r="A14" s="13" t="inlineStr">
         <is>
           <t>Аудитор</t>
         </is>
       </c>
-      <c r="B14" s="16" t="inlineStr">
-        <is>
-          <t>только чтение журналов и истории изменений</t>
-        </is>
-      </c>
-      <c r="C14" s="16" t="inlineStr">
+      <c r="B14" s="13" t="inlineStr">
+        <is>
+          <t>только чтение журналов и истории</t>
+        </is>
+      </c>
+      <c r="C14" s="13" t="inlineStr">
         <is>
           <t>весь контур, read-only</t>
         </is>
       </c>
-      <c r="D14" s="16" t="inlineStr">
+      <c r="D14" s="13" t="inlineStr">
         <is>
           <t>нет</t>
         </is>
       </c>
-      <c r="E14" s="16" t="inlineStr">
+      <c r="E14" s="13" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="F14" s="16" t="inlineStr">
+      <c r="F14" s="13" t="inlineStr">
         <is>
           <t>неприменимо</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="16" t="inlineStr">
+      <c r="A15" s="13" t="inlineStr">
         <is>
           <t>Читатель</t>
         </is>
       </c>
-      <c r="B15" s="16" t="inlineStr">
+      <c r="B15" s="13" t="inlineStr">
         <is>
           <t>просмотр по уровню доступа</t>
         </is>
       </c>
-      <c r="C15" s="16" t="inlineStr">
+      <c r="C15" s="13" t="inlineStr">
         <is>
           <t>по конфиденциальности документа</t>
         </is>
       </c>
-      <c r="D15" s="16" t="inlineStr">
+      <c r="D15" s="13" t="inlineStr">
         <is>
           <t>нет</t>
         </is>
       </c>
-      <c r="E15" s="16" t="inlineStr">
+      <c r="E15" s="13" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="F15" s="16" t="inlineStr">
+      <c r="F15" s="13" t="inlineStr">
         <is>
           <t>неприменимо</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="16" t="inlineStr">
+      <c r="A16" s="13" t="inlineStr">
         <is>
           <t>ИИ-агент</t>
         </is>
       </c>
-      <c r="B16" s="16" t="inlineStr">
-        <is>
-          <t>предлагает: origin='предложено ИИ', verification='не проверено', approval='не направлено', lifecycle='черновик'</t>
-        </is>
-      </c>
-      <c r="C16" s="16" t="inlineStr">
+      <c r="B16" s="13" t="inlineStr">
+        <is>
+          <t>в целевой модели предлагает: origin/verification/approval/lifecycle только начальные значения</t>
+        </is>
+      </c>
+      <c r="C16" s="13" t="inlineStr">
         <is>
           <t>любой объект, куда подключён</t>
         </is>
       </c>
-      <c r="D16" s="16" t="inlineStr">
+      <c r="D16" s="13" t="inlineStr">
         <is>
           <t>нет</t>
         </is>
       </c>
-      <c r="E16" s="16" t="inlineStr">
+      <c r="E16" s="13" t="inlineStr">
         <is>
           <t>нет</t>
         </is>
       </c>
-      <c r="F16" s="16" t="inlineStr">
-        <is>
-          <t>неприменимо — ИИ не может согласовывать/утверждать ничего, включая собственные предложения</t>
+      <c r="F16" s="13" t="inlineStr">
+        <is>
+          <t>неприменимо в целевой модели</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="17" t="inlineStr">
-        <is>
-          <t>Неизменяемый журнал утверждений:</t>
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>Неизменяемый журнал утверждений (целевое требование, не реализовано):</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>— каждое действие 'согласовано'/'утверждено'/'отклонено' пишется в append-only журнал (без возможности редактирования задним числом);</t>
+          <t>— каждое действие 'согласовано'/'утверждено'/'отклонено' пишется в append-only журнал;</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>— запись журнала содержит: кто, когда, по какой роли, в рамках какой области полномочий, было ли это делегирование или замещение;</t>
+          <t>— запись журнала содержит: кто, когда, по какой роли, область полномочий, делегирование/замещение;</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>— срок действия роли хранится отдельно от факта присвоения роли (роль может быть неактивна, но история не удаляется);</t>
+          <t>— срок действия роли хранится отдельно от факта присвоения роли;</t>
         </is>
       </c>
     </row>
@@ -3763,378 +4513,432 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="42" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
     <col width="55" customWidth="1" min="4" max="4"/>
     <col width="30" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="10" t="inlineStr">
+      <c r="A1" s="7" t="inlineStr">
         <is>
           <t>Модель безопасности RAG — факт по уровням (модуль / инфраструктура)</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="11" t="inlineStr">
-        <is>
-          <t>Отсутствие механизма В МОДУЛЕ exec-knowledge не означает отсутствие компенсирующих мер на других уровнях — уровни разделены явно</t>
+      <c r="A2" s="8" t="inlineStr">
+        <is>
+          <t>Строка 'исключение из передачи AI-провайдеру' — не предположение, а подтверждённый факт кода (лист 11)</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="12" t="inlineStr">
+      <c r="A4" s="9" t="inlineStr">
         <is>
           <t>Контрольная точка</t>
         </is>
       </c>
-      <c r="B4" s="12" t="inlineStr">
+      <c r="B4" s="9" t="inlineStr">
         <is>
           <t>Уровень проверки</t>
         </is>
       </c>
-      <c r="C4" s="12" t="inlineStr">
+      <c r="C4" s="9" t="inlineStr">
         <is>
           <t>Статус</t>
         </is>
       </c>
-      <c r="D4" s="12" t="inlineStr">
+      <c r="D4" s="9" t="inlineStr">
         <is>
           <t>Комментарий</t>
         </is>
       </c>
-      <c r="E4" s="12" t="inlineStr">
+      <c r="E4" s="9" t="inlineStr">
         <is>
           <t>Риск</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="16" t="inlineStr">
+      <c r="A5" s="13" t="inlineStr">
         <is>
           <t>Классификация конфиденциальности документа</t>
         </is>
       </c>
-      <c r="B5" s="16" t="inlineStr">
+      <c r="B5" s="13" t="inlineStr">
         <is>
           <t>Модуль exec-knowledge</t>
         </is>
       </c>
-      <c r="C5" s="15" t="inlineStr">
+      <c r="C5" s="12" t="inlineStr">
         <is>
           <t>не обнаружено</t>
         </is>
       </c>
-      <c r="D5" s="16" t="inlineStr">
-        <is>
-          <t>Проверено по исходному коду backend/exec-knowledge/index.py — поле и логика отсутствуют</t>
-        </is>
-      </c>
-      <c r="E5" s="15" t="inlineStr">
+      <c r="D5" s="13" t="inlineStr">
+        <is>
+          <t>Проверено по исходному коду — поле и логика отсутствуют</t>
+        </is>
+      </c>
+      <c r="E5" s="12" t="inlineStr">
         <is>
           <t>высокий</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="16" t="inlineStr">
+      <c r="A6" s="13" t="inlineStr">
         <is>
           <t>Классификация конфиденциальности документа</t>
         </is>
       </c>
-      <c r="B6" s="16" t="inlineStr">
+      <c r="B6" s="13" t="inlineStr">
         <is>
           <t>Общесистемный / инфраструктурный уровень</t>
         </is>
       </c>
-      <c r="C6" s="13" t="inlineStr">
+      <c r="C6" s="10" t="inlineStr">
         <is>
           <t>требует проверки</t>
         </is>
       </c>
-      <c r="D6" s="16" t="inlineStr">
-        <is>
-          <t>Не проверялось: возможна компенсация через общую политику доступа к кабинету</t>
-        </is>
-      </c>
-      <c r="E6" s="16" t="inlineStr">
+      <c r="D6" s="13" t="inlineStr">
+        <is>
+          <t>Не проверялось</t>
+        </is>
+      </c>
+      <c r="E6" s="13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="16" t="inlineStr">
+      <c r="A7" s="13" t="inlineStr">
         <is>
           <t>Разграничение доступа на уровне документа</t>
         </is>
       </c>
-      <c r="B7" s="16" t="inlineStr">
+      <c r="B7" s="13" t="inlineStr">
         <is>
           <t>Модуль exec-knowledge</t>
         </is>
       </c>
-      <c r="C7" s="15" t="inlineStr">
+      <c r="C7" s="12" t="inlineStr">
         <is>
           <t>не обнаружено</t>
         </is>
       </c>
-      <c r="D7" s="16" t="inlineStr">
+      <c r="D7" s="13" t="inlineStr">
         <is>
           <t>Доступ определяется общей ролью кабинета (exec_cabinet_access), не документом</t>
         </is>
       </c>
-      <c r="E7" s="15" t="inlineStr">
+      <c r="E7" s="12" t="inlineStr">
         <is>
           <t>высокий</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="16" t="inlineStr">
+      <c r="A8" s="13" t="inlineStr">
         <is>
           <t>Разграничение доступа на уровне документа</t>
         </is>
       </c>
-      <c r="B8" s="16" t="inlineStr">
+      <c r="B8" s="13" t="inlineStr">
         <is>
           <t>Row Level Security в БД</t>
         </is>
       </c>
-      <c r="C8" s="13" t="inlineStr">
+      <c r="C8" s="10" t="inlineStr">
         <is>
           <t>требует проверки</t>
         </is>
       </c>
-      <c r="D8" s="16" t="inlineStr">
+      <c r="D8" s="13" t="inlineStr">
         <is>
           <t>Не проверялось напрямую через системные каталоги PostgreSQL</t>
         </is>
       </c>
-      <c r="E8" s="16" t="inlineStr">
+      <c r="E8" s="13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="16" t="inlineStr">
+      <c r="A9" s="13" t="inlineStr">
         <is>
           <t>Журнал обращений (чтения) к документам</t>
         </is>
       </c>
-      <c r="B9" s="16" t="inlineStr">
+      <c r="B9" s="13" t="inlineStr">
         <is>
           <t>Модуль exec-knowledge / exec_audit_log</t>
         </is>
       </c>
-      <c r="C9" s="15" t="inlineStr">
+      <c r="C9" s="12" t="inlineStr">
         <is>
           <t>не обнаружено</t>
         </is>
       </c>
-      <c r="D9" s="16" t="inlineStr">
+      <c r="D9" s="13" t="inlineStr">
         <is>
           <t>exec_audit_log фиксирует create/update/delete, не чтение</t>
         </is>
       </c>
-      <c r="E9" s="13" t="inlineStr">
+      <c r="E9" s="10" t="inlineStr">
         <is>
           <t>средний</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="16" t="inlineStr">
+      <c r="A10" s="13" t="inlineStr">
         <is>
           <t>Журнал обращений (чтения) к документам</t>
         </is>
       </c>
-      <c r="B10" s="16" t="inlineStr">
-        <is>
-          <t>Инфраструктурный уровень (access-логи API Gateway)</t>
-        </is>
-      </c>
-      <c r="C10" s="13" t="inlineStr">
+      <c r="B10" s="13" t="inlineStr">
+        <is>
+          <t>Инфраструктурный уровень (access-логи)</t>
+        </is>
+      </c>
+      <c r="C10" s="10" t="inlineStr">
         <is>
           <t>требует проверки</t>
         </is>
       </c>
-      <c r="D10" s="16" t="inlineStr">
+      <c r="D10" s="13" t="inlineStr">
         <is>
           <t>Не проверялось — вне зоны доступа песочницы</t>
         </is>
       </c>
-      <c r="E10" s="16" t="inlineStr">
+      <c r="E10" s="13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="16" t="inlineStr">
+      <c r="A11" s="13" t="inlineStr">
         <is>
           <t>Исключение закрытых документов из общего поиска</t>
         </is>
       </c>
-      <c r="B11" s="16" t="inlineStr">
+      <c r="B11" s="13" t="inlineStr">
         <is>
           <t>Модуль exec-knowledge</t>
         </is>
       </c>
-      <c r="C11" s="15" t="inlineStr">
+      <c r="C11" s="12" t="inlineStr">
         <is>
           <t>не обнаружено</t>
         </is>
       </c>
-      <c r="D11" s="16" t="inlineStr">
-        <is>
-          <t>Признака confidentiality/is_confidential в схеме exec_knowledge нет</t>
-        </is>
-      </c>
-      <c r="E11" s="15" t="inlineStr">
+      <c r="D11" s="13" t="inlineStr">
+        <is>
+          <t>Признака confidentiality в схеме нет</t>
+        </is>
+      </c>
+      <c r="E11" s="12" t="inlineStr">
         <is>
           <t>высокий</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="16" t="inlineStr">
+      <c r="A12" s="13" t="inlineStr">
+        <is>
+          <t>Исключение из передачи AI-провайдеру (payload YandexGPT)</t>
+        </is>
+      </c>
+      <c r="B12" s="13" t="inlineStr">
+        <is>
+          <t>Модуль exec-planner-ai</t>
+        </is>
+      </c>
+      <c r="C12" s="11" t="inlineStr">
+        <is>
+          <t>НЕ ОБНАРУЖЕНО — подтверждено фактом</t>
+        </is>
+      </c>
+      <c r="D12" s="13" t="inlineStr">
+        <is>
+          <t>Фильтр только use_in_ai=true AND status='active'; все 6 записей проходят фильтр. См. лист 11</t>
+        </is>
+      </c>
+      <c r="E12" s="12" t="inlineStr">
+        <is>
+          <t>критический</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="13" t="inlineStr">
+        <is>
+          <t>Журнал запросов к AI-провайдеру</t>
+        </is>
+      </c>
+      <c r="B13" s="13" t="inlineStr">
+        <is>
+          <t>Модуль exec-planner-ai</t>
+        </is>
+      </c>
+      <c r="C13" s="12" t="inlineStr">
+        <is>
+          <t>не обнаружено</t>
+        </is>
+      </c>
+      <c r="D13" s="13" t="inlineStr">
+        <is>
+          <t>Нет ни БД-таблицы, ни logger/print в коде. get_logs не вернул записей</t>
+        </is>
+      </c>
+      <c r="E13" s="12" t="inlineStr">
+        <is>
+          <t>высокий</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="13" t="inlineStr">
         <is>
           <t>Шифрование данных в хранилище</t>
         </is>
       </c>
-      <c r="B12" s="16" t="inlineStr">
-        <is>
-          <t>S3-совместимое хранилище (bucket.poehali.dev)</t>
-        </is>
-      </c>
-      <c r="C12" s="13" t="inlineStr">
+      <c r="B14" s="13" t="inlineStr">
+        <is>
+          <t>S3-совместимое хранилище</t>
+        </is>
+      </c>
+      <c r="C14" s="10" t="inlineStr">
         <is>
           <t>требует проверки</t>
         </is>
       </c>
-      <c r="D12" s="16" t="inlineStr">
-        <is>
-          <t>Информация от провайдера не запрашивалась в рамках данного пакета</t>
-        </is>
-      </c>
-      <c r="E12" s="13" t="inlineStr">
+      <c r="D14" s="13" t="inlineStr">
+        <is>
+          <t>Информация от провайдера не запрашивалась</t>
+        </is>
+      </c>
+      <c r="E14" s="10" t="inlineStr">
         <is>
           <t>средний</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="16" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="13" t="inlineStr">
         <is>
           <t>Общая авторизация доступа к кабинету</t>
         </is>
       </c>
-      <c r="B13" s="16" t="inlineStr">
+      <c r="B15" s="13" t="inlineStr">
         <is>
           <t>Модуль auth / exec_cabinet_access</t>
         </is>
       </c>
-      <c r="C13" s="14" t="inlineStr">
+      <c r="C15" s="11" t="inlineStr">
         <is>
           <t>подтверждено</t>
         </is>
       </c>
-      <c r="D13" s="16" t="inlineStr">
-        <is>
-          <t>Сессионная авторизация и таблица допуска exec_cabinet_access существуют и используются</t>
-        </is>
-      </c>
-      <c r="E13" s="16" t="inlineStr">
+      <c r="D15" s="13" t="inlineStr">
+        <is>
+          <t>Сессионная авторизация существует и используется</t>
+        </is>
+      </c>
+      <c r="E15" s="13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="16" t="inlineStr">
-        <is>
-          <t>Сроки хранения и порядок удаления документов</t>
-        </is>
-      </c>
-      <c r="B14" s="16" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="13" t="inlineStr">
+        <is>
+          <t>Сроки хранения и удаления документов</t>
+        </is>
+      </c>
+      <c r="B16" s="13" t="inlineStr">
         <is>
           <t>Вся платформа</t>
         </is>
       </c>
-      <c r="C14" s="18" t="inlineStr">
+      <c r="C16" s="14" t="inlineStr">
         <is>
           <t>не применяется</t>
         </is>
       </c>
-      <c r="D14" s="16" t="inlineStr">
-        <is>
-          <t>Политика хранения не описана ни в коде, ни в документации проекта</t>
-        </is>
-      </c>
-      <c r="E14" s="13" t="inlineStr">
+      <c r="D16" s="13" t="inlineStr">
+        <is>
+          <t>Политика хранения не описана</t>
+        </is>
+      </c>
+      <c r="E16" s="10" t="inlineStr">
         <is>
           <t>средний</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="16" t="inlineStr">
-        <is>
-          <t>DLP / защита от массовой выгрузки контента</t>
-        </is>
-      </c>
-      <c r="B15" s="16" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="13" t="inlineStr">
+        <is>
+          <t>DLP / защита от массовой выгрузки</t>
+        </is>
+      </c>
+      <c r="B17" s="13" t="inlineStr">
         <is>
           <t>Модуль exec-knowledge</t>
         </is>
       </c>
-      <c r="C15" s="15" t="inlineStr">
+      <c r="C17" s="12" t="inlineStr">
         <is>
           <t>не обнаружено</t>
         </is>
       </c>
-      <c r="D15" s="16" t="inlineStr">
-        <is>
-          <t>API отдаёт полный body без постраничного ограничения за один запрос</t>
-        </is>
-      </c>
-      <c r="E15" s="13" t="inlineStr">
+      <c r="D17" s="13" t="inlineStr">
+        <is>
+          <t>API отдаёт полный body без ограничения объёма за запрос</t>
+        </is>
+      </c>
+      <c r="E17" s="10" t="inlineStr">
         <is>
           <t>средний</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="16" t="inlineStr">
-        <is>
-          <t>Запрет использования запросов/документов для обучения внешней модели</t>
-        </is>
-      </c>
-      <c r="B16" s="16" t="inlineStr">
-        <is>
-          <t>AI-провайдер (внешний контур)</t>
-        </is>
-      </c>
-      <c r="C16" s="13" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="13" t="inlineStr">
+        <is>
+          <t>Запрет использования запросов для обучения внешней модели</t>
+        </is>
+      </c>
+      <c r="B18" s="13" t="inlineStr">
+        <is>
+          <t>AI-провайдер YandexGPT</t>
+        </is>
+      </c>
+      <c r="C18" s="10" t="inlineStr">
         <is>
           <t>требует проверки</t>
         </is>
       </c>
-      <c r="D16" s="16" t="inlineStr">
-        <is>
-          <t>Провайдер, тариф, договорные условия, регион обработки, субпроцессоры — не установлены в рамках пакета</t>
-        </is>
-      </c>
-      <c r="E16" s="15" t="inlineStr">
-        <is>
-          <t>критический — блокирующий (см. ADR-003)</t>
+      <c r="D18" s="13" t="inlineStr">
+        <is>
+          <t>Тариф, договорные условия, регион обработки, субпроцессоры — не установлены</t>
+        </is>
+      </c>
+      <c r="E18" s="12" t="inlineStr">
+        <is>
+          <t>критический — блокирующий</t>
         </is>
       </c>
     </row>

--- a/public/model/v1/current/knowledge_model_package_v1.xlsx
+++ b/public/model/v1/current/knowledge_model_package_v1.xlsx
@@ -22,6 +22,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12.Issue Register" sheetId="13" state="visible" r:id="rId13"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="13.Risk Register" sheetId="14" state="visible" r:id="rId14"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="14.Границы этапа 1" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="15.Инцидент RR-001" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="16.Алгоритм pick_knowledge" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="17.Источники аудита" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="18.Вопрос ключа YandexGPT" sheetId="19" state="visible" r:id="rId19"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -31,7 +35,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="10">
+  <fonts count="12">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -77,6 +81,14 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00B85450"/>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="7">
@@ -138,7 +150,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -166,6 +178,12 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -551,7 +569,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
@@ -615,7 +632,6 @@
         </is>
       </c>
     </row>
-    <row r="13"/>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
@@ -637,7 +653,6 @@
         </is>
       </c>
     </row>
-    <row r="17"/>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
@@ -673,7 +688,6 @@
         </is>
       </c>
     </row>
-    <row r="23"/>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
@@ -702,7 +716,6 @@
         </is>
       </c>
     </row>
-    <row r="28"/>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
@@ -731,7 +744,6 @@
         </is>
       </c>
     </row>
-    <row r="33"/>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
@@ -795,7 +807,6 @@
         </is>
       </c>
     </row>
-    <row r="43"/>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
@@ -838,7 +849,6 @@
         </is>
       </c>
     </row>
-    <row r="50"/>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
@@ -895,7 +905,6 @@
         </is>
       </c>
     </row>
-    <row r="59"/>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
@@ -2119,34 +2128,34 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="13" t="inlineStr">
+      <c r="A5" s="12" t="inlineStr">
         <is>
           <t>RR-001</t>
         </is>
       </c>
-      <c r="B5" s="13" t="inlineStr">
-        <is>
-          <t>Внутренние документы Банка технически доступны внешнему AI-провайдеру (YandexGPT) без ограничения по конфиденциальности</t>
+      <c r="B5" s="12" t="inlineStr">
+        <is>
+          <t>Внутренние документы Банка МОГЛИ БЫТЬ технически доступны внешнему AI-провайдеру (YandexGPT) без ограничения по конфиденциальности. СДЕРЖИВАНИЕ ВЫПОЛНЕНО 2026-09-11: use_in_ai=false для всех 6 записей, проверено локально — выборка pick_knowledge возвращает 0 строк. Факт прошлой передачи НЕ подтверждён и НЕ опровергнут (журнал запросов отсутствует, см. лист 17).</t>
         </is>
       </c>
       <c r="C5" s="12" t="inlineStr">
         <is>
-          <t>Критический</t>
-        </is>
-      </c>
-      <c r="D5" s="13" t="inlineStr">
+          <t>Критический — СДЕРЖАН, расследование открыто</t>
+        </is>
+      </c>
+      <c r="D5" s="12" t="inlineStr">
         <is>
           <t>Все 6 записей exec_knowledge, включая реальный ВНД (№6)</t>
         </is>
       </c>
-      <c r="E5" s="13" t="inlineStr">
+      <c r="E5" s="12" t="inlineStr">
         <is>
           <t>Руководитель + ИБ</t>
         </is>
       </c>
-      <c r="F5" s="13" t="inlineStr">
-        <is>
-          <t>Временно снять use_in_ai с №6 вручную; реализовать confidentiality-фильтр (ADR-006); получить ответ провайдера по обучению на данных (лист 11)</t>
+      <c r="F5" s="12" t="inlineStr">
+        <is>
+          <t>Выполнено: экстренное use_in_ai=false (лист 15). Открыто: проверить биллинг YandexGPT на факт прошлых обращений (лист 17); реализовать confidentiality-фильтр (ADR-006) до повторного включения; решение о ротации ключа — за владельцем (лист 18)</t>
         </is>
       </c>
     </row>
@@ -2551,6 +2560,1212 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F33"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="55" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>Журнал экстренного сдерживания по RR-001</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="8" t="inlineStr">
+        <is>
+          <t>Аварийная мера выполнена 2026-09-11. Тексты, чанки, статусы записей не изменялись. Удаление не выполнялось.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="15" t="inlineStr">
+        <is>
+          <t>Идентификатор инцидента</t>
+        </is>
+      </c>
+      <c r="B4" s="16" t="inlineStr">
+        <is>
+          <t>INC-001 (связан с RR-001)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="15" t="inlineStr">
+        <is>
+          <t>Дата и время обнаружения</t>
+        </is>
+      </c>
+      <c r="B5" s="16" t="inlineStr">
+        <is>
+          <t>2026-09-11, в ходе read-only аудита AI-маршрута (пакет v2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="15" t="inlineStr">
+        <is>
+          <t>Классификация</t>
+        </is>
+      </c>
+      <c r="B6" s="16" t="inlineStr">
+        <is>
+          <t>Потенциальный риск передачи внутренних материалов во внешний AI-контур без документной классификации конфиденциальности. Факт прошлой передачи НЕ подтверждён и НЕ опровергнут — журнал недоступен.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="15" t="inlineStr">
+        <is>
+          <t>Решение о сдерживании принято</t>
+        </is>
+      </c>
+      <c r="B7" s="16" t="inlineStr">
+        <is>
+          <t>Владелец кабинета, 2026-09-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="15" t="inlineStr">
+        <is>
+          <t>Формулировка основания</t>
+        </is>
+      </c>
+      <c r="B8" s="16" t="inlineStr">
+        <is>
+          <t>«Экстренное ограничение использования материалов в AI-контексте до определения их конфиденциальности, допустимости обработки в YandexGPT и принятия решения по RR-001»</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>СНИМОК ДО / ПОСЛЕ</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="17" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B11" s="17" t="inlineStr">
+        <is>
+          <t>Название</t>
+        </is>
+      </c>
+      <c r="C11" s="17" t="inlineStr">
+        <is>
+          <t>use_in_ai ДО</t>
+        </is>
+      </c>
+      <c r="D11" s="17" t="inlineStr">
+        <is>
+          <t>use_in_ai ПОСЛЕ</t>
+        </is>
+      </c>
+      <c r="E11" s="17" t="inlineStr">
+        <is>
+          <t>Чанков</t>
+        </is>
+      </c>
+      <c r="F11" s="17" t="inlineStr">
+        <is>
+          <t>Приоритет</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="B12" s="13" t="inlineStr">
+        <is>
+          <t>Матрица стейкхолдеров по этапам инициативы</t>
+        </is>
+      </c>
+      <c r="C12" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="D12" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="E12" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="F12" s="13" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="B13" s="13" t="inlineStr">
+        <is>
+          <t>О создании рабочей группы по мониторингу и координации реализации проектов портфеля Блока внутреннего контроля</t>
+        </is>
+      </c>
+      <c r="C13" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="D13" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="E13" s="13" t="n">
+        <v>31</v>
+      </c>
+      <c r="F13" s="13" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="B14" s="13" t="inlineStr">
+        <is>
+          <t>Обоснование создания ЦЦиРТКД</t>
+        </is>
+      </c>
+      <c r="C14" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="D14" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="E14" s="13" t="n">
+        <v>9</v>
+      </c>
+      <c r="F14" s="13" t="n">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="B15" s="13" t="inlineStr">
+        <is>
+          <t>Роль CDS Блока внутреннего контроля (Кузьменко А.В.)</t>
+        </is>
+      </c>
+      <c r="C15" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="D15" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="E15" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="F15" s="13" t="n">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="B16" s="13" t="inlineStr">
+        <is>
+          <t>Концепция роли CDS (официальный документ Банка)</t>
+        </is>
+      </c>
+      <c r="C16" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="D16" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="E16" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="F16" s="13" t="n">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="B17" s="13" t="inlineStr">
+        <is>
+          <t>Положение о Департаменте внутреннего контроля и комплаенса (проект, на согласование)</t>
+        </is>
+      </c>
+      <c r="C17" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="D17" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="E17" s="13" t="n">
+        <v>13</v>
+      </c>
+      <c r="F17" s="13" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>ХРОНОЛОГИЯ ОПЕРАЦИИ (UTC)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="17" t="inlineStr">
+        <is>
+          <t>Время</t>
+        </is>
+      </c>
+      <c r="B20" s="17" t="inlineStr">
+        <is>
+          <t>Действие</t>
+        </is>
+      </c>
+      <c r="C20" s="17" t="inlineStr">
+        <is>
+          <t>Метод</t>
+        </is>
+      </c>
+      <c r="D20" s="17" t="inlineStr">
+        <is>
+          <t>Результат</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="13" t="inlineStr">
+        <is>
+          <t>18:44:25</t>
+        </is>
+      </c>
+      <c r="B21" s="13" t="inlineStr">
+        <is>
+          <t>Read-only снимок 6 записей exec_knowledge (значения ДО)</t>
+        </is>
+      </c>
+      <c r="C21" s="13" t="inlineStr">
+        <is>
+          <t>SQL SELECT (read-only)</t>
+        </is>
+      </c>
+      <c r="D21" s="13" t="inlineStr">
+        <is>
+          <t>6 записей, все use_in_ai=true — зафиксировано</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="13" t="inlineStr">
+        <is>
+          <t>18:45:06</t>
+        </is>
+      </c>
+      <c r="B22" s="13" t="inlineStr">
+        <is>
+          <t>Экстренное ограничение: use_in_ai=false для id 1-6</t>
+        </is>
+      </c>
+      <c r="C22" s="13" t="inlineStr">
+        <is>
+          <t>SQL UPDATE, функционально идентичный action=toggle_ai backend/exec-knowledge (миграция V0352, т.к. у агента нет пользовательской HTTP-сессии для вызова API как актора)</t>
+        </is>
+      </c>
+      <c r="D22" s="13" t="inlineStr">
+        <is>
+          <t>6 записей обновлены, тексты/статусы/заголовки не изменены</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="13" t="inlineStr">
+        <is>
+          <t>18:45:xx</t>
+        </is>
+      </c>
+      <c r="B23" s="13" t="inlineStr">
+        <is>
+          <t>Read-only проверка выборки pick_knowledge (основная ветка)</t>
+        </is>
+      </c>
+      <c r="C23" s="13" t="inlineStr">
+        <is>
+          <t>SQL SELECT, идентичный коду exec-planner-ai, БЕЗ вызова YandexGPT</t>
+        </is>
+      </c>
+      <c r="D23" s="13" t="inlineStr">
+        <is>
+          <t>0 строк — ни одна запись не проходит фильтр</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="13" t="inlineStr">
+        <is>
+          <t>18:45:xx</t>
+        </is>
+      </c>
+      <c r="B24" s="13" t="inlineStr">
+        <is>
+          <t>Read-only проверка выборки pick_knowledge (fallback-ветка)</t>
+        </is>
+      </c>
+      <c r="C24" s="13" t="inlineStr">
+        <is>
+          <t>SQL SELECT, идентичный коду exec-planner-ai, БЕЗ вызова YandexGPT</t>
+        </is>
+      </c>
+      <c r="D24" s="13" t="inlineStr">
+        <is>
+          <t>0 строк — fallback тоже не находит записей</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="13" t="inlineStr">
+        <is>
+          <t>18:45:xx</t>
+        </is>
+      </c>
+      <c r="B25" s="13" t="inlineStr">
+        <is>
+          <t>Проверка backend/exec-knowledge, backend/exec-planner-ai логов</t>
+        </is>
+      </c>
+      <c r="C25" s="13" t="inlineStr">
+        <is>
+          <t>get_logs (платформенный инструмент)</t>
+        </is>
+      </c>
+      <c r="D25" s="13" t="inlineStr">
+        <is>
+          <t>0 записей — история за пределами короткого текущего окна недоступна этим инструментом</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="18" t="inlineStr">
+        <is>
+          <t>ВАЖНО: НЕ ВЫПОЛНЕНО НА ЭТОМ ШАГЕ (по прямому запрету)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>— тестовый запрос к YandexGPT НЕ отправлялся;</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>— документы, чанки, статусы, заголовки НЕ изменялись, кроме use_in_ai;</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>— миграции структуры, индексы, архитектура НЕ менялись;</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>— новые ВНД НЕ загружались;</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>— use_in_ai НЕ включён обратно;</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>— ключ YANDEX_GPT_API_KEY НЕ менялся и НЕ ротировался — решение за владельцем (см. лист 16).</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="B4:F4"/>
+    <mergeCell ref="A33:F33"/>
+    <mergeCell ref="B7:F7"/>
+    <mergeCell ref="A28:F28"/>
+    <mergeCell ref="B6:F6"/>
+    <mergeCell ref="A32:F32"/>
+    <mergeCell ref="B5:F5"/>
+    <mergeCell ref="A31:F31"/>
+    <mergeCell ref="B8:F8"/>
+    <mergeCell ref="A30:F30"/>
+    <mergeCell ref="A29:F29"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="38" customWidth="1" min="1" max="1"/>
+    <col width="55" customWidth="1" min="2" max="2"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>Точный алгоритм выборки — исправление формулировки 'передавались все документы целиком'</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="8" t="inlineStr">
+        <is>
+          <t>Утверждение из v2 было неточным: технически мог отбираться любой поднабор бюджета в 7000 символов / 8 фрагментов, а не гарантированно 'все документы полностью'</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="9" t="inlineStr">
+        <is>
+          <t>Параметр</t>
+        </is>
+      </c>
+      <c r="B4" s="9" t="inlineStr">
+        <is>
+          <t>Установленное значение (по коду)</t>
+        </is>
+      </c>
+      <c r="C4" s="9" t="inlineStr">
+        <is>
+          <t>Комментарий</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="13" t="inlineStr">
+        <is>
+          <t>Источник выборки</t>
+        </is>
+      </c>
+      <c r="B5" s="13" t="inlineStr">
+        <is>
+          <t>exec_knowledge JOIN exec_knowledge_chunk</t>
+        </is>
+      </c>
+      <c r="C5" s="13" t="inlineStr">
+        <is>
+          <t>Только записи с use_in_ai=true AND status='active' (сейчас: 0 из 6)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="13" t="inlineStr">
+        <is>
+          <t>LIMIT в основном запросе</t>
+        </is>
+      </c>
+      <c r="B6" s="13" t="inlineStr">
+        <is>
+          <t>1500 строк чанков (не документов)</t>
+        </is>
+      </c>
+      <c r="C6" s="13" t="inlineStr">
+        <is>
+          <t>Верхний предел кандидатов до скоринга, не гарантия отбора всех</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="13" t="inlineStr">
+        <is>
+          <t>Алгоритм отбора</t>
+        </is>
+      </c>
+      <c r="B7" s="13" t="inlineStr">
+        <is>
+          <t>Скоринг по совпадению слов запроса в content и title + бонус за priority</t>
+        </is>
+      </c>
+      <c r="C7" s="13" t="inlineStr">
+        <is>
+          <t>Не является семантическим поиском; простое совпадение подстрок</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="13" t="inlineStr">
+        <is>
+          <t>Сколько чанков реально уходит в промпт</t>
+        </is>
+      </c>
+      <c r="B8" s="13" t="inlineStr">
+        <is>
+          <t>До 8 фрагментов ИЛИ пока не превышен бюджет символов</t>
+        </is>
+      </c>
+      <c r="C8" s="13" t="inlineStr">
+        <is>
+          <t>Что наступит раньше — то и останавливает отбор</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="13" t="inlineStr">
+        <is>
+          <t>Бюджет объёма контекста</t>
+        </is>
+      </c>
+      <c r="B9" s="13" t="inlineStr">
+        <is>
+          <t>KNOWLEDGE_BUDGET = 7000 символов суммарно</t>
+        </is>
+      </c>
+      <c r="C9" s="13" t="inlineStr">
+        <is>
+          <t>Не 7000 на документ — общий предел на весь блок регламентов в промпте</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="13" t="inlineStr">
+        <is>
+          <t>Fallback-ветка (если совпадений нет)</t>
+        </is>
+      </c>
+      <c r="B10" s="13" t="inlineStr">
+        <is>
+          <t>6 чанков с наибольшим priority, ORDER BY priority DESC, chunk_index</t>
+        </is>
+      </c>
+      <c r="C10" s="13" t="inlineStr">
+        <is>
+          <t>Тоже ограничена тем же фильтром use_in_ai/status — при новом состоянии вернёт 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="13" t="inlineStr">
+        <is>
+          <t>Может ли один запрос затронуть все 6 документов одновременно</t>
+        </is>
+      </c>
+      <c r="B11" s="13" t="inlineStr">
+        <is>
+          <t>Технически да, если по каждому есть хоть слабое совпадение и суммарно укладывается в 7000 симв. и 8 фрагментов</t>
+        </is>
+      </c>
+      <c r="C11" s="13" t="inlineStr">
+        <is>
+          <t>НЕ означает, что так происходило по факту — не установлено без журнала</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="13" t="inlineStr">
+        <is>
+          <t>Передаётся ли текст урезанным</t>
+        </is>
+      </c>
+      <c r="B12" s="13" t="inlineStr">
+        <is>
+          <t>Нет, каждый отобранный чанк — content.strip() целиком</t>
+        </is>
+      </c>
+      <c r="C12" s="13" t="inlineStr">
+        <is>
+          <t>Урезание влияет только на КОЛИЧЕСТВО отобранных чанков, не на их содержимое</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
+    <col width="46" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>Проверенные и непроверенные источники для расследования факта прошлых передач</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="8" t="inlineStr">
+        <is>
+          <t>Рекомендация: биллинг YandexGPT — самый быстрый способ подтвердить ФАКТ обращений (по расходу), даже без деталей содержимого запросов</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="9" t="inlineStr">
+        <is>
+          <t>Источник</t>
+        </is>
+      </c>
+      <c r="B4" s="9" t="inlineStr">
+        <is>
+          <t>Доступность агенту</t>
+        </is>
+      </c>
+      <c r="C4" s="9" t="inlineStr">
+        <is>
+          <t>Период хранения</t>
+        </is>
+      </c>
+      <c r="D4" s="9" t="inlineStr">
+        <is>
+          <t>Что удалось установить</t>
+        </is>
+      </c>
+      <c r="E4" s="9" t="inlineStr">
+        <is>
+          <t>Чего установить невозможно</t>
+        </is>
+      </c>
+      <c r="F4" s="9" t="inlineStr">
+        <is>
+          <t>Что нужно для проверки</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="13" t="inlineStr">
+        <is>
+          <t>get_logs (backend/exec-knowledge, backend/exec-planner-ai)</t>
+        </is>
+      </c>
+      <c r="B5" s="11" t="inlineStr">
+        <is>
+          <t>Доступен агенту</t>
+        </is>
+      </c>
+      <c r="C5" s="13" t="inlineStr">
+        <is>
+          <t>Короткое текущее окно (минуты/часы)</t>
+        </is>
+      </c>
+      <c r="D5" s="13" t="inlineStr">
+        <is>
+          <t>0 записей на момент проверки</t>
+        </is>
+      </c>
+      <c r="E5" s="13" t="inlineStr">
+        <is>
+          <t>История вызовов ДО текущего окна — недоступна</t>
+        </is>
+      </c>
+      <c r="F5" s="13" t="inlineStr">
+        <is>
+          <t>Не проверялось — доступ вне инструментов агента</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="13" t="inlineStr">
+        <is>
+          <t>get_logs (frontend)</t>
+        </is>
+      </c>
+      <c r="B6" s="11" t="inlineStr">
+        <is>
+          <t>Доступен агенту</t>
+        </is>
+      </c>
+      <c r="C6" s="13" t="inlineStr">
+        <is>
+          <t>~5-10 минут на момент проверки</t>
+        </is>
+      </c>
+      <c r="D6" s="13" t="inlineStr">
+        <is>
+          <t>Обращений к exec-planner-ai не зафиксировано в этом окне</t>
+        </is>
+      </c>
+      <c r="E6" s="13" t="inlineStr">
+        <is>
+          <t>Более ранние клиентские события</t>
+        </is>
+      </c>
+      <c r="F6" s="13" t="inlineStr">
+        <is>
+          <t>Не проверялось</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="13" t="inlineStr">
+        <is>
+          <t>Метрики облачной функции (частота вызовов, длительность)</t>
+        </is>
+      </c>
+      <c r="B7" s="10" t="inlineStr">
+        <is>
+          <t>Не проверялось</t>
+        </is>
+      </c>
+      <c r="C7" s="13" t="inlineStr">
+        <is>
+          <t>неизвестен</t>
+        </is>
+      </c>
+      <c r="D7" s="13" t="inlineStr">
+        <is>
+          <t>не установлено</t>
+        </is>
+      </c>
+      <c r="E7" s="13" t="inlineStr">
+        <is>
+          <t>не установлено</t>
+        </is>
+      </c>
+      <c r="F7" s="13" t="inlineStr">
+        <is>
+          <t>Требуются права уровня владельца облачного аккаунта poehali.dev</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="13" t="inlineStr">
+        <is>
+          <t>API Gateway (маршрутизация, статусы ответов)</t>
+        </is>
+      </c>
+      <c r="B8" s="10" t="inlineStr">
+        <is>
+          <t>Не проверялось</t>
+        </is>
+      </c>
+      <c r="C8" s="13" t="inlineStr">
+        <is>
+          <t>неизвестен</t>
+        </is>
+      </c>
+      <c r="D8" s="13" t="inlineStr">
+        <is>
+          <t>не установлено</t>
+        </is>
+      </c>
+      <c r="E8" s="13" t="inlineStr">
+        <is>
+          <t>не установлено</t>
+        </is>
+      </c>
+      <c r="F8" s="13" t="inlineStr">
+        <is>
+          <t>Вне зоны доступа инструментов агента</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="13" t="inlineStr">
+        <is>
+          <t>Аудит-журналы Yandex Cloud (сервисный аккаунт)</t>
+        </is>
+      </c>
+      <c r="B9" s="10" t="inlineStr">
+        <is>
+          <t>Не проверялось</t>
+        </is>
+      </c>
+      <c r="C9" s="13" t="inlineStr">
+        <is>
+          <t>неизвестен</t>
+        </is>
+      </c>
+      <c r="D9" s="13" t="inlineStr">
+        <is>
+          <t>не установлено</t>
+        </is>
+      </c>
+      <c r="E9" s="13" t="inlineStr">
+        <is>
+          <t>не установлено</t>
+        </is>
+      </c>
+      <c r="F9" s="13" t="inlineStr">
+        <is>
+          <t>Требуется доступ к консоли Yandex Cloud владельца ключа YANDEX_GPT_API_KEY</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="13" t="inlineStr">
+        <is>
+          <t>Биллинг / потребление YandexGPT (Yandex Cloud Billing)</t>
+        </is>
+      </c>
+      <c r="B10" s="10" t="inlineStr">
+        <is>
+          <t>Не проверялось</t>
+        </is>
+      </c>
+      <c r="C10" s="13" t="inlineStr">
+        <is>
+          <t>обычно длительный</t>
+        </is>
+      </c>
+      <c r="D10" s="13" t="inlineStr">
+        <is>
+          <t>не установлено</t>
+        </is>
+      </c>
+      <c r="E10" s="13" t="inlineStr">
+        <is>
+          <t>не установлено</t>
+        </is>
+      </c>
+      <c r="F10" s="13" t="inlineStr">
+        <is>
+          <t>Косвенно мог бы подтвердить ФАКТ обращений (по расходу токенов) даже без деталей содержимого — рекомендуется проверить в первую очередь</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="13" t="inlineStr">
+        <is>
+          <t>История операций сервисной учётной записи (IAM Yandex Cloud)</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>Не проверялось</t>
+        </is>
+      </c>
+      <c r="C11" s="13" t="inlineStr">
+        <is>
+          <t>неизвестен</t>
+        </is>
+      </c>
+      <c r="D11" s="13" t="inlineStr">
+        <is>
+          <t>не установлено</t>
+        </is>
+      </c>
+      <c r="E11" s="13" t="inlineStr">
+        <is>
+          <t>не установлено</t>
+        </is>
+      </c>
+      <c r="F11" s="13" t="inlineStr">
+        <is>
+          <t>Требуется доступ владельца облачного аккаунта</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="13" t="inlineStr">
+        <is>
+          <t>Сетевые/инфраструктурные журналы платформы poehali.dev</t>
+        </is>
+      </c>
+      <c r="B12" s="10" t="inlineStr">
+        <is>
+          <t>Не проверялось</t>
+        </is>
+      </c>
+      <c r="C12" s="13" t="inlineStr">
+        <is>
+          <t>неизвестен</t>
+        </is>
+      </c>
+      <c r="D12" s="13" t="inlineStr">
+        <is>
+          <t>не установлено</t>
+        </is>
+      </c>
+      <c r="E12" s="13" t="inlineStr">
+        <is>
+          <t>не установлено</t>
+        </is>
+      </c>
+      <c r="F12" s="13" t="inlineStr">
+        <is>
+          <t>Вне зоны доступа инструментов агента — запрос к поддержке платформы</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="13" t="inlineStr">
+        <is>
+          <t>SIEM / резервные журналы</t>
+        </is>
+      </c>
+      <c r="B13" s="10" t="inlineStr">
+        <is>
+          <t>Не проверялось</t>
+        </is>
+      </c>
+      <c r="C13" s="13" t="inlineStr">
+        <is>
+          <t>неизвестен</t>
+        </is>
+      </c>
+      <c r="D13" s="13" t="inlineStr">
+        <is>
+          <t>существование не подтверждено</t>
+        </is>
+      </c>
+      <c r="E13" s="13" t="inlineStr">
+        <is>
+          <t>не установлено</t>
+        </is>
+      </c>
+      <c r="F13" s="13" t="inlineStr">
+        <is>
+          <t>Неизвестно, развёрнут ли SIEM для этого проекта</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="13" t="inlineStr">
+        <is>
+          <t>exec_audit_log (БД проекта)</t>
+        </is>
+      </c>
+      <c r="B14" s="11" t="inlineStr">
+        <is>
+          <t>Проверено</t>
+        </is>
+      </c>
+      <c r="C14" s="13" t="inlineStr">
+        <is>
+          <t>с момента внедрения таблицы</t>
+        </is>
+      </c>
+      <c r="D14" s="13" t="inlineStr">
+        <is>
+          <t>toggle_ai НЕ пишет в этот журнал (проверено по коду) — прошлые переключения use_in_ai не отражены</t>
+        </is>
+      </c>
+      <c r="E14" s="13" t="inlineStr">
+        <is>
+          <t>любые действия ДО внедрения таблицы аудита</t>
+        </is>
+      </c>
+      <c r="F14" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="55" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="70" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>Проверка обстоятельств вокруг API-ключа (без ротации на этом шаге)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="8" t="inlineStr">
+        <is>
+          <t>Ключ НЕ ротирован. Значение ключа не раскрывалось агентом ни в одном выводе — проверено</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="9" t="inlineStr">
+        <is>
+          <t>Вопрос</t>
+        </is>
+      </c>
+      <c r="B4" s="9" t="inlineStr">
+        <is>
+          <t>Установлено</t>
+        </is>
+      </c>
+      <c r="C4" s="9" t="inlineStr">
+        <is>
+          <t>Комментарий</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="13" t="inlineStr">
+        <is>
+          <t>Отображалось ли значение ключа YANDEX_GPT_API_KEY в переписке, логах или выводе инструментов этой сессии</t>
+        </is>
+      </c>
+      <c r="B5" s="13" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="C5" s="13" t="inlineStr">
+        <is>
+          <t>Инструмент get_secrets возвращает только имена и описания секретов, не значения — проверено: значение ключа ни разу не запрашивалось и не выводилось в этой работе</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="13" t="inlineStr">
+        <is>
+          <t>Используется ли ключ другими функциями платформы, кроме exec-planner-ai</t>
+        </is>
+      </c>
+      <c r="B6" s="13" t="inlineStr">
+        <is>
+          <t>Требует проверки</t>
+        </is>
+      </c>
+      <c r="C6" s="13" t="inlineStr">
+        <is>
+          <t>Секрет YANDEX_GPT_API_KEY общий для проекта; какие ещё backend-функции реально его читают — не проверялось построчно в этом аудите</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="13" t="inlineStr">
+        <is>
+          <t>Дата создания ключа</t>
+        </is>
+      </c>
+      <c r="B7" s="13" t="inlineStr">
+        <is>
+          <t>не установлено</t>
+        </is>
+      </c>
+      <c r="C7" s="13" t="inlineStr">
+        <is>
+          <t>Требует проверки в консоли Yandex Cloud владельцем аккаунта</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="13" t="inlineStr">
+        <is>
+          <t>Ограничения по сервisной учётной записи (права, квоты)</t>
+        </is>
+      </c>
+      <c r="B8" s="13" t="inlineStr">
+        <is>
+          <t>не установлено</t>
+        </is>
+      </c>
+      <c r="C8" s="13" t="inlineStr">
+        <is>
+          <t>Требует проверки в IAM Yandex Cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="13" t="inlineStr">
+        <is>
+          <t>Можно ли выпустить отдельный ключ для кабинета ЦЦиРТКД</t>
+        </is>
+      </c>
+      <c r="B9" s="13" t="inlineStr">
+        <is>
+          <t>не установлено</t>
+        </is>
+      </c>
+      <c r="C9" s="13" t="inlineStr">
+        <is>
+          <t>Организационный вопрос к владельцу облачного аккаунта</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="13" t="inlineStr">
+        <is>
+          <t>Рекомендация по ротации</t>
+        </is>
+      </c>
+      <c r="B10" s="13" t="inlineStr">
+        <is>
+          <t>Ротация НЕ выполнена на этом шаге</t>
+        </is>
+      </c>
+      <c r="C10" s="13" t="inlineStr">
+        <is>
+          <t>Ключ не считается раскрытым по имеющимся у агента данным (см. первую строку) — значит, экстренной ротации по факту утечки самого ключа не требуется. Решение о плановой ротации — за владельцем, вне рамок read-only аудита</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -2570,7 +3785,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
@@ -2620,7 +3834,6 @@
         </is>
       </c>
     </row>
-    <row r="10"/>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
@@ -2663,7 +3876,6 @@
         </is>
       </c>
     </row>
-    <row r="17"/>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
@@ -2692,7 +3904,6 @@
         </is>
       </c>
     </row>
-    <row r="22"/>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
@@ -2714,7 +3925,6 @@
         </is>
       </c>
     </row>
-    <row r="26"/>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
